--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -48,85 +48,85 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
   </si>
   <si>
     <t>!StatInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionType_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionValue_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionType_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionValue_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SkillOption_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>SkillOption_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ATK_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>DEF_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaxHP_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Accuracy_Add</t>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Armor</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Accessory</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>EquipmentType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -143,43 +143,43 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Accessory</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>EquipmentTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>GradeTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!GradeTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -196,7 +196,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -213,266 +213,254 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>철검</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>철검(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>철검(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(노말)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>철검(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>철검(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionType_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionValue_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(노말)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MATK_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CritRate_Add</t>
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Class_Ranged</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Class_Mage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BindCharacter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 장갑</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(일반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Block_Add</t>
@@ -488,15 +476,15 @@
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!EquipmentTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -513,163 +501,183 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Craft</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material_01_Count</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material_01_ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material_02_ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material_02_Count</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material_03_ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material_03_Count</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무활</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(노말)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무활(매직)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무활(레어)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무활(에픽)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나무활(레전드)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Enchant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>EnchantInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionType_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionType_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaxEnchantLv</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Probability</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CostType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CostValue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>UnlockLv</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>UnlockSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Ruby</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CostLvModify</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ProbabilityLvModify</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Result_EquipmentID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyCost_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyCost_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionValue_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionValue_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -835,13 +843,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -851,45 +859,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,7 +1181,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1307,7 +1315,7 @@
       <c r="B30" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1366,10 +1374,10 @@
         <v>25</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>7</v>
@@ -1384,10 +1392,10 @@
         <v>11</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>12</v>
@@ -1411,34 +1419,34 @@
         <v>36</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>9</v>
@@ -1456,7 +1464,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>20</v>
@@ -1465,7 +1473,7 @@
         <v>29</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I4" s="1">
         <v>10001</v>
@@ -1505,7 +1513,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
@@ -1540,7 +1548,7 @@
         <v>31</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I6" s="1">
         <v>10001</v>
@@ -1566,7 +1574,7 @@
         <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>20</v>
@@ -1575,7 +1583,7 @@
         <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1">
         <v>10001</v>
@@ -1587,7 +1595,7 @@
         <v>25</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M7" s="1">
         <v>0.4</v>
@@ -1601,7 +1609,7 @@
         <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>20</v>
@@ -1610,7 +1618,7 @@
         <v>33</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1">
         <v>10001</v>
@@ -1634,10 +1642,10 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>20</v>
@@ -1646,7 +1654,7 @@
         <v>29</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I9" s="1">
         <v>10002</v>
@@ -1658,7 +1666,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9" s="7">
         <v>5</v>
@@ -1674,10 +1682,10 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
@@ -1686,7 +1694,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I10" s="1">
         <v>10002</v>
@@ -1698,7 +1706,7 @@
         <v>25</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M10" s="1">
         <v>10</v>
@@ -1710,10 +1718,10 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>20</v>
@@ -1722,7 +1730,7 @@
         <v>31</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I11" s="1">
         <v>10002</v>
@@ -1734,7 +1742,7 @@
         <v>30</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M11" s="1">
         <v>15</v>
@@ -1745,10 +1753,10 @@
         <v>100009</v>
       </c>
       <c r="C12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>20</v>
@@ -1757,7 +1765,7 @@
         <v>32</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I12" s="1">
         <v>10002</v>
@@ -1769,7 +1777,7 @@
         <v>35</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M12" s="1">
         <v>20</v>
@@ -1780,10 +1788,10 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>20</v>
@@ -1792,7 +1800,7 @@
         <v>33</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I13" s="1">
         <v>10002</v>
@@ -1804,7 +1812,7 @@
         <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M13" s="1">
         <v>25</v>
@@ -1816,10 +1824,10 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>20</v>
@@ -1828,13 +1836,13 @@
         <v>29</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I14" s="1">
         <v>10003</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K14" s="7">
         <v>15</v>
@@ -1856,10 +1864,10 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>20</v>
@@ -1868,13 +1876,13 @@
         <v>30</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I15" s="1">
         <v>10003</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K15" s="1">
         <v>20</v>
@@ -1891,10 +1899,10 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>20</v>
@@ -1903,13 +1911,13 @@
         <v>31</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I16" s="1">
         <v>10003</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K16" s="1">
         <v>25</v>
@@ -1926,10 +1934,10 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>20</v>
@@ -1938,13 +1946,13 @@
         <v>32</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I17" s="1">
         <v>10003</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K17" s="1">
         <v>30</v>
@@ -1962,10 +1970,10 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
@@ -1974,13 +1982,13 @@
         <v>33</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I18" s="1">
         <v>10003</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K18" s="1">
         <v>35</v>
@@ -1999,10 +2007,10 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>21</v>
@@ -2026,10 +2034,10 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="1" t="s">
@@ -2055,10 +2063,10 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>21</v>
@@ -2082,10 +2090,10 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>21</v>
@@ -2109,10 +2117,10 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>21</v>
@@ -2137,10 +2145,10 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>21</v>
@@ -2164,10 +2172,10 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="1" t="s">
@@ -2193,10 +2201,10 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>21</v>
@@ -2220,10 +2228,10 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>21</v>
@@ -2247,10 +2255,10 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>21</v>
@@ -2275,10 +2283,10 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>21</v>
@@ -2290,7 +2298,7 @@
         <v>20003</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K29" s="1">
         <v>0.02</v>
@@ -2302,10 +2310,10 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="1" t="s">
@@ -2319,7 +2327,7 @@
         <v>20003</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K30" s="1">
         <v>0.04</v>
@@ -2331,10 +2339,10 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>21</v>
@@ -2346,7 +2354,7 @@
         <v>20003</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K31" s="1">
         <v>0.06</v>
@@ -2358,10 +2366,10 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>21</v>
@@ -2373,7 +2381,7 @@
         <v>20003</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K32" s="1">
         <v>0.08</v>
@@ -2385,10 +2393,10 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>21</v>
@@ -2400,7 +2408,7 @@
         <v>20003</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
@@ -2412,10 +2420,10 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>21</v>
@@ -2427,7 +2435,7 @@
         <v>20004</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K34" s="1">
         <v>20</v>
@@ -2438,10 +2446,10 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="1" t="s">
@@ -2455,7 +2463,7 @@
         <v>20004</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K35" s="1">
         <v>25</v>
@@ -2466,10 +2474,10 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>21</v>
@@ -2481,7 +2489,7 @@
         <v>20004</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -2492,10 +2500,10 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>21</v>
@@ -2507,7 +2515,7 @@
         <v>20004</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K37" s="1">
         <v>40</v>
@@ -2518,10 +2526,10 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>21</v>
@@ -2533,7 +2541,7 @@
         <v>20004</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K38" s="1">
         <v>50</v>
@@ -2545,10 +2553,10 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>21</v>
@@ -2560,7 +2568,7 @@
         <v>20005</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
@@ -2571,10 +2579,10 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="1" t="s">
@@ -2588,7 +2596,7 @@
         <v>20005</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2599,10 +2607,10 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>21</v>
@@ -2614,7 +2622,7 @@
         <v>20005</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K41" s="1">
         <v>3</v>
@@ -2625,10 +2633,10 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>21</v>
@@ -2640,7 +2648,7 @@
         <v>20005</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K42" s="1">
         <v>4</v>
@@ -2651,10 +2659,10 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>21</v>
@@ -2666,7 +2674,7 @@
         <v>20005</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K43" s="1">
         <v>5</v>
@@ -2677,10 +2685,10 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>22</v>
@@ -2703,10 +2711,10 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
@@ -2730,10 +2738,10 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
@@ -2757,10 +2765,10 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>22</v>
@@ -2784,10 +2792,10 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>22</v>
@@ -2811,10 +2819,10 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>22</v>
@@ -2826,7 +2834,7 @@
         <v>30002</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K49" s="1">
         <v>10</v>
@@ -2837,10 +2845,10 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>22</v>
@@ -2853,7 +2861,7 @@
         <v>30002</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K50" s="1">
         <v>20</v>
@@ -2864,10 +2872,10 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
@@ -2880,7 +2888,7 @@
         <v>30002</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K51" s="1">
         <v>30</v>
@@ -2891,10 +2899,10 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>22</v>
@@ -2906,7 +2914,7 @@
         <v>30002</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K52" s="1">
         <v>40</v>
@@ -2917,10 +2925,10 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>22</v>
@@ -2932,7 +2940,7 @@
         <v>30002</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K53" s="1">
         <v>50</v>
@@ -2943,10 +2951,10 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>22</v>
@@ -2958,7 +2966,7 @@
         <v>30003</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K54" s="1">
         <v>2.5</v>
@@ -2969,10 +2977,10 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>22</v>
@@ -2984,7 +2992,7 @@
         <v>30003</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K55" s="1">
         <v>5</v>
@@ -2995,10 +3003,10 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>22</v>
@@ -3010,7 +3018,7 @@
         <v>30003</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K56" s="1">
         <v>10</v>
@@ -3021,10 +3029,10 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>22</v>
@@ -3036,7 +3044,7 @@
         <v>30003</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K57" s="1">
         <v>12</v>
@@ -3047,10 +3055,10 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>22</v>
@@ -3062,7 +3070,7 @@
         <v>30003</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K58" s="1">
         <v>15</v>
@@ -3096,7 +3104,7 @@
       <c r="A65" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3128,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3137,40 +3145,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="G2" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3179,40 +3187,40 @@
         <v>4</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3224,7 +3232,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3258,7 +3266,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3292,7 +3300,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3307,7 +3315,7 @@
         <v>-0.02</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -3326,7 +3334,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3360,7 +3368,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3394,7 +3402,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3409,7 +3417,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3427,7 +3435,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3442,7 +3450,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3456,7 +3464,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3471,7 +3479,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3485,7 +3493,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3514,7 +3522,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3529,7 +3537,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3543,7 +3551,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3558,7 +3566,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -3577,7 +3585,7 @@
       <c r="I18" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3609,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -3623,37 +3631,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>143</v>
-      </c>
       <c r="H2" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -3662,37 +3670,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -3762,7 +3770,7 @@
       <c r="N18" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="147">
   <si>
     <t>!Table</t>
   </si>
@@ -657,6 +657,10 @@
   </si>
   <si>
     <t>철검(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(일반)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2286,7 +2290,7 @@
         <v>56</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>21</v>
@@ -3100,8 +3104,8 @@
       <c r="F64"/>
       <c r="Q64" s="1"/>
     </row>
-    <row r="65" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
+    <row r="65" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q65" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -129,6 +129,516 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>Accessory</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipmentTypes</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatOptionType_3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatOptionValue_3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Add</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+  </si>
+  <si>
+    <t>!CharacterTypes</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Ranged</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BindCharacter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 방패</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 방패(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 방패(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 방패(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 방패(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 방패(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 반지</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 반지(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 반지(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 반지(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 반지(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 반지(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 목걸이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 귀걸이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 목걸이(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 목걸이(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 목걸이(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 목걸이(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 목걸이(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 귀걸이(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 귀걸이(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 귀걸이(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 귀걸이(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 귀걸이(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EquipmentTypes</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_01_Count</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_01_ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_02_ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_02_Count</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_03_ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_03_Count</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활(매직)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활(레어)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활(에픽)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활(레전드)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enchant</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnchantInfo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StepStatOptionType_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StepStatOptionType_2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxEnchantLv</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Probability</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostValue</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockLv</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockSkill</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruby</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostLvModify</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProbabilityLvModify</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result_EquipmentID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyCost_01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyCost_02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StepStatOptionValue_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StepStatOptionValue_2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 투구(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무지팡이(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무활(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 갑옷(일반)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>G</t>
     </r>
@@ -146,521 +656,11 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Accessory</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>EquipmentTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>GradeTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magic</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Epic</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!GradeTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>con</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>string</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatOptionType_3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatOptionValue_3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-  </si>
-  <si>
-    <t>!CharacterTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Melee</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Ranged</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Mage</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>BindCharacter</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Add</t>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EquipmentTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>int</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Craft</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material_01_Count</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material_01_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material_02_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material_02_Count</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material_03_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material_03_Count</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enchant</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnchantInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>StepStatOptionType_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>StepStatOptionType_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxEnchantLv</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Probability</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CurrencyInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CostType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CostValue</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnlockLv</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnlockSkill</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruby</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CostLvModify</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProbabilityLvModify</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result_EquipmentID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyType_01</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyCost_01</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyType_02</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyCost_02</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>StepStatOptionValue_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>StepStatOptionValue_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(일반)</t>
+    <t>ItemGradeTypes</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ItemGradeTypes</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -855,7 +855,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -902,6 +902,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1185,7 +1188,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1210,7 +1213,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1225,7 +1228,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1233,32 +1236,32 @@
         <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1335,7 +1338,7 @@
     <col min="4" max="4" width="19.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.375" style="1" customWidth="1"/>
     <col min="10" max="10" width="18.875" style="1" bestFit="1" customWidth="1"/>
@@ -1369,19 +1372,19 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>25</v>
+      <c r="G2" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>7</v>
@@ -1396,10 +1399,10 @@
         <v>11</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>12</v>
@@ -1420,37 +1423,37 @@
         <v>5</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>34</v>
+        <v>102</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>9</v>
@@ -1465,19 +1468,19 @@
         <v>100001</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1">
         <v>10001</v>
@@ -1505,19 +1508,19 @@
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
@@ -1540,19 +1543,19 @@
         <v>100003</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1">
         <v>10001</v>
@@ -1575,19 +1578,19 @@
         <v>100004</v>
       </c>
       <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1">
         <v>10001</v>
@@ -1599,7 +1602,7 @@
         <v>25</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M7" s="1">
         <v>0.4</v>
@@ -1610,19 +1613,19 @@
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I8" s="1">
         <v>10001</v>
@@ -1646,19 +1649,19 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I9" s="1">
         <v>10002</v>
@@ -1670,7 +1673,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M9" s="7">
         <v>5</v>
@@ -1686,19 +1689,19 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I10" s="1">
         <v>10002</v>
@@ -1710,7 +1713,7 @@
         <v>25</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M10" s="1">
         <v>10</v>
@@ -1722,19 +1725,19 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I11" s="1">
         <v>10002</v>
@@ -1746,7 +1749,7 @@
         <v>30</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M11" s="1">
         <v>15</v>
@@ -1757,19 +1760,19 @@
         <v>100009</v>
       </c>
       <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I12" s="1">
         <v>10002</v>
@@ -1781,7 +1784,7 @@
         <v>35</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M12" s="1">
         <v>20</v>
@@ -1792,19 +1795,19 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I13" s="1">
         <v>10002</v>
@@ -1816,7 +1819,7 @@
         <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M13" s="1">
         <v>25</v>
@@ -1828,25 +1831,25 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I14" s="1">
         <v>10003</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K14" s="7">
         <v>15</v>
@@ -1868,25 +1871,25 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I15" s="1">
         <v>10003</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K15" s="1">
         <v>20</v>
@@ -1903,25 +1906,25 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I16" s="1">
         <v>10003</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K16" s="1">
         <v>25</v>
@@ -1938,25 +1941,25 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I17" s="1">
         <v>10003</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K17" s="1">
         <v>30</v>
@@ -1974,25 +1977,25 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I18" s="1">
         <v>10003</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K18" s="1">
         <v>35</v>
@@ -2011,16 +2014,16 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I19" s="1">
         <v>20001</v>
@@ -2038,17 +2041,17 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="1">
@@ -2067,16 +2070,16 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I21" s="1">
         <v>20001</v>
@@ -2094,16 +2097,16 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1">
         <v>20001</v>
@@ -2121,16 +2124,16 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I23" s="1">
         <v>20001</v>
@@ -2149,16 +2152,16 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1">
         <v>20002</v>
@@ -2176,17 +2179,17 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="1">
@@ -2205,16 +2208,16 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I26" s="1">
         <v>20002</v>
@@ -2232,16 +2235,16 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I27" s="1">
         <v>20002</v>
@@ -2259,16 +2262,16 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I28" s="1">
         <v>20002</v>
@@ -2287,22 +2290,22 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I29" s="1">
         <v>20003</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K29" s="1">
         <v>0.02</v>
@@ -2314,24 +2317,24 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="1">
         <v>20003</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K30" s="1">
         <v>0.04</v>
@@ -2343,22 +2346,22 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I31" s="1">
         <v>20003</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K31" s="1">
         <v>0.06</v>
@@ -2370,22 +2373,22 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I32" s="1">
         <v>20003</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K32" s="1">
         <v>0.08</v>
@@ -2397,22 +2400,22 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I33" s="1">
         <v>20003</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
@@ -2424,22 +2427,22 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I34" s="1">
         <v>20004</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K34" s="1">
         <v>20</v>
@@ -2450,24 +2453,24 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="1">
         <v>20004</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K35" s="1">
         <v>25</v>
@@ -2478,22 +2481,22 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I36" s="1">
         <v>20004</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -2504,22 +2507,22 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I37" s="1">
         <v>20004</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K37" s="1">
         <v>40</v>
@@ -2530,22 +2533,22 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I38" s="1">
         <v>20004</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K38" s="1">
         <v>50</v>
@@ -2557,22 +2560,22 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I39" s="1">
         <v>20005</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
@@ -2583,24 +2586,24 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="1">
         <v>20005</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2611,22 +2614,22 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I41" s="1">
         <v>20005</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K41" s="1">
         <v>3</v>
@@ -2637,22 +2640,22 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I42" s="1">
         <v>20005</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K42" s="1">
         <v>4</v>
@@ -2663,22 +2666,22 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I43" s="1">
         <v>20005</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K43" s="1">
         <v>5</v>
@@ -2689,16 +2692,16 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I44" s="1">
         <v>30001</v>
@@ -2715,16 +2718,16 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I45" s="1">
         <v>30001</v>
@@ -2742,16 +2745,16 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I46" s="1">
         <v>30001</v>
@@ -2769,16 +2772,16 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I47" s="1">
         <v>30001</v>
@@ -2796,16 +2799,16 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I48" s="1">
         <v>30001</v>
@@ -2823,22 +2826,22 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I49" s="1">
         <v>30002</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K49" s="1">
         <v>10</v>
@@ -2849,23 +2852,23 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="1">
         <v>30002</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K50" s="1">
         <v>20</v>
@@ -2876,23 +2879,23 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="1">
         <v>30002</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K51" s="1">
         <v>30</v>
@@ -2903,22 +2906,22 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I52" s="1">
         <v>30002</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K52" s="1">
         <v>40</v>
@@ -2929,22 +2932,22 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I53" s="1">
         <v>30002</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K53" s="1">
         <v>50</v>
@@ -2955,22 +2958,22 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I54" s="1">
         <v>30003</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K54" s="1">
         <v>2.5</v>
@@ -2981,22 +2984,22 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I55" s="1">
         <v>30003</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K55" s="1">
         <v>5</v>
@@ -3007,22 +3010,22 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I56" s="1">
         <v>30003</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K56" s="1">
         <v>10</v>
@@ -3033,22 +3036,22 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I57" s="1">
         <v>30003</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K57" s="1">
         <v>12</v>
@@ -3059,22 +3062,22 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I58" s="1">
         <v>30003</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K58" s="1">
         <v>15</v>
@@ -3140,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3149,40 +3152,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3191,40 +3194,40 @@
         <v>4</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3236,7 +3239,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3270,7 +3273,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3304,7 +3307,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3319,7 +3322,7 @@
         <v>-0.02</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -3338,7 +3341,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3372,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3406,7 +3409,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3421,7 +3424,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3439,7 +3442,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3454,7 +3457,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3468,7 +3471,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3483,7 +3486,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3497,7 +3500,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3526,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3541,7 +3544,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3555,7 +3558,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3570,7 +3573,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -3621,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -3635,37 +3638,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>139</v>
-      </c>
       <c r="H2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>110</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -3674,37 +3677,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="160">
   <si>
     <t>!Table</t>
   </si>
@@ -48,113 +48,109 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
   </si>
   <si>
     <t>!StatInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionType_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionValue_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionType_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionValue_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SkillOption_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SkillOption_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ATK_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>DEF_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MaxHP_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Accuracy_Add</t>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Armor</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Accessory</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EquipmentType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Accessory</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>EquipmentTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -171,7 +167,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -188,254 +184,254 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>철검</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>철검(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>철검(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>철검(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>철검(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionType_3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StatOptionValue_3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MATK_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CritRate_Add</t>
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Ranged</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Mage</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BindCharacter</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 장갑</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 갑옷(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무 방패(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 신발(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 반지(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 목걸이(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>구리 귀걸이(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Block_Add</t>
@@ -451,15 +447,15 @@
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!EquipmentTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -476,167 +472,163 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Craft</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Material_01_Count</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Material_01_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Material_02_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Material_02_Count</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Material_03_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Material_03_Count</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무활</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무활(매직)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무활(레어)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무활(에픽)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무활(레전드)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Enchant</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EnchantInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionType_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionType_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MaxEnchantLv</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Probability</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CostType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CostValue</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>UnlockLv</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>UnlockSkill</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Ruby</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CostLvModify</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ProbabilityLvModify</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Result_EquipmentID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_01</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyCost_01</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_02</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyCost_02</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionValue_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StepStatOptionValue_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>가죽 투구(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무지팡이(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>나무활(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>철검(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(일반)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -653,27 +645,88 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ItemGradeTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipmentTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Sword</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Bow</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Hammer</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Helmet</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Armor</t>
+  </si>
+  <si>
+    <t>가죽 장갑</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑(일반)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑(매직)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑(레어)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑(에픽)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑(레전드)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Shield_Metal</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Ring</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -847,13 +900,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -863,48 +916,48 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1213,7 +1266,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1236,32 +1289,32 @@
         <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1322,7 +1375,7 @@
       <c r="B30" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1336,7 +1389,7 @@
     <col min="2" max="2" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
@@ -1372,19 +1425,19 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>7</v>
@@ -1399,10 +1452,10 @@
         <v>11</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>12</v>
@@ -1423,37 +1476,37 @@
         <v>5</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>9</v>
@@ -1468,19 +1521,22 @@
         <v>100001</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I4" s="1">
         <v>10001</v>
@@ -1508,19 +1564,22 @@
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
@@ -1543,19 +1602,22 @@
         <v>100003</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>35</v>
+      <c r="E6" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6" s="1">
         <v>10001</v>
@@ -1578,19 +1640,22 @@
         <v>100004</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I7" s="1">
         <v>10001</v>
@@ -1602,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M7" s="1">
         <v>0.4</v>
@@ -1613,19 +1678,22 @@
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I8" s="1">
         <v>10001</v>
@@ -1649,19 +1717,22 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I9" s="1">
         <v>10002</v>
@@ -1673,7 +1744,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M9" s="7">
         <v>5</v>
@@ -1689,19 +1760,22 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>113</v>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I10" s="1">
         <v>10002</v>
@@ -1713,7 +1787,7 @@
         <v>25</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M10" s="1">
         <v>10</v>
@@ -1725,19 +1799,22 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I11" s="1">
         <v>10002</v>
@@ -1749,7 +1826,7 @@
         <v>30</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M11" s="1">
         <v>15</v>
@@ -1760,19 +1837,22 @@
         <v>100009</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1">
         <v>10002</v>
@@ -1784,7 +1864,7 @@
         <v>35</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M12" s="1">
         <v>20</v>
@@ -1795,19 +1875,22 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1">
         <v>10002</v>
@@ -1819,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M13" s="1">
         <v>25</v>
@@ -1831,25 +1914,28 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1">
         <v>10003</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" s="7">
         <v>15</v>
@@ -1871,25 +1957,28 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>42</v>
+      <c r="E15" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" s="1">
         <v>10003</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K15" s="1">
         <v>20</v>
@@ -1906,25 +1995,28 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I16" s="1">
         <v>10003</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K16" s="1">
         <v>25</v>
@@ -1941,25 +2033,28 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I17" s="1">
         <v>10003</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K17" s="1">
         <v>30</v>
@@ -1977,25 +2072,28 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I18" s="1">
         <v>10003</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K18" s="1">
         <v>35</v>
@@ -2014,16 +2112,19 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I19" s="1">
         <v>20001</v>
@@ -2041,17 +2142,19 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="1">
@@ -2070,16 +2173,19 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I21" s="1">
         <v>20001</v>
@@ -2097,16 +2203,19 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22" s="1">
         <v>20001</v>
@@ -2124,16 +2233,19 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="1">
         <v>20001</v>
@@ -2152,16 +2264,19 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I24" s="1">
         <v>20002</v>
@@ -2179,17 +2294,19 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="12"/>
+        <v>59</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="F25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="1">
@@ -2208,16 +2325,19 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I26" s="1">
         <v>20002</v>
@@ -2235,16 +2355,19 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>63</v>
+      <c r="E27" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I27" s="1">
         <v>20002</v>
@@ -2262,16 +2385,19 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1">
         <v>20002</v>
@@ -2290,22 +2416,25 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I29" s="1">
         <v>20003</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K29" s="1">
         <v>0.02</v>
@@ -2317,24 +2446,26 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="12"/>
+        <v>153</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="F30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="1">
         <v>20003</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K30" s="1">
         <v>0.04</v>
@@ -2346,22 +2477,25 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>61</v>
+        <v>154</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I31" s="1">
         <v>20003</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K31" s="1">
         <v>0.06</v>
@@ -2373,22 +2507,25 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>63</v>
+        <v>155</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I32" s="1">
         <v>20003</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K32" s="1">
         <v>0.08</v>
@@ -2400,22 +2537,25 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>64</v>
+        <v>156</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I33" s="1">
         <v>20003</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
@@ -2427,22 +2567,25 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>66</v>
+      <c r="E34" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I34" s="1">
         <v>20004</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K34" s="1">
         <v>20</v>
@@ -2453,24 +2596,26 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="F35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="1">
         <v>20004</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K35" s="1">
         <v>25</v>
@@ -2481,22 +2626,25 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I36" s="1">
         <v>20004</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -2507,22 +2655,25 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I37" s="1">
         <v>20004</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K37" s="1">
         <v>40</v>
@@ -2533,22 +2684,25 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I38" s="1">
         <v>20004</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K38" s="1">
         <v>50</v>
@@ -2560,22 +2714,25 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>72</v>
+      <c r="E39" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I39" s="1">
         <v>20005</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
@@ -2586,24 +2743,26 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="1">
         <v>20005</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2614,22 +2773,25 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I41" s="1">
         <v>20005</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K41" s="1">
         <v>3</v>
@@ -2640,22 +2802,25 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I42" s="1">
         <v>20005</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K42" s="1">
         <v>4</v>
@@ -2666,22 +2831,25 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" s="1">
         <v>20005</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K43" s="1">
         <v>5</v>
@@ -2692,16 +2860,19 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>78</v>
+      <c r="E44" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I44" s="1">
         <v>30001</v>
@@ -2718,16 +2889,19 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I45" s="1">
         <v>30001</v>
@@ -2745,16 +2919,19 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I46" s="1">
         <v>30001</v>
@@ -2772,16 +2949,19 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I47" s="1">
         <v>30001</v>
@@ -2799,16 +2979,19 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I48" s="1">
         <v>30001</v>
@@ -2826,22 +3009,25 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I49" s="1">
         <v>30002</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K49" s="1">
         <v>10</v>
@@ -2852,23 +3038,26 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="1">
         <v>30002</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K50" s="1">
         <v>20</v>
@@ -2879,23 +3068,26 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="1">
         <v>30002</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K51" s="1">
         <v>30</v>
@@ -2906,22 +3098,25 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1">
         <v>30002</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K52" s="1">
         <v>40</v>
@@ -2932,22 +3127,25 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I53" s="1">
         <v>30002</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K53" s="1">
         <v>50</v>
@@ -2958,22 +3156,25 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I54" s="1">
         <v>30003</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K54" s="1">
         <v>2.5</v>
@@ -2984,22 +3185,25 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I55" s="1">
         <v>30003</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K55" s="1">
         <v>5</v>
@@ -3010,22 +3214,25 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I56" s="1">
         <v>30003</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K56" s="1">
         <v>10</v>
@@ -3036,22 +3243,25 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I57" s="1">
         <v>30003</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K57" s="1">
         <v>12</v>
@@ -3062,22 +3272,25 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I58" s="1">
         <v>30003</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K58" s="1">
         <v>15</v>
@@ -3111,7 +3324,7 @@
       <c r="Q65" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3143,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3152,40 +3365,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="H2" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3194,40 +3407,40 @@
         <v>4</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3239,7 +3452,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3273,7 +3486,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3307,7 +3520,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3322,7 +3535,7 @@
         <v>-0.02</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -3341,7 +3554,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3375,7 +3588,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3409,7 +3622,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3424,7 +3637,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3442,7 +3655,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3457,7 +3670,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3471,7 +3684,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3486,7 +3699,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3500,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3529,7 +3742,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3544,7 +3757,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3558,7 +3771,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3573,7 +3786,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -3592,7 +3805,7 @@
       <c r="I18" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3624,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -3638,37 +3851,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>136</v>
-      </c>
       <c r="H2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>109</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -3677,37 +3890,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -3777,7 +3990,7 @@
       <c r="N18" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="208">
   <si>
     <t>!Table</t>
   </si>
@@ -58,14 +58,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>StatOptionType_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatOptionValue_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -75,10 +67,6 @@
   </si>
   <si>
     <t>StatOptionValue_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillOption_1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -187,26 +175,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>철검</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>StatOptionType_3</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -215,26 +183,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>나무지팡이</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>MATK_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -259,174 +207,6 @@
   </si>
   <si>
     <t>BindCharacter</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 갑옷(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 방패(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 반지(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 목걸이(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 귀걸이(레전드)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -507,26 +287,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>나무활</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Enchant</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -612,22 +372,6 @@
   </si>
   <si>
     <t>StepStatOptionValue_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 투구(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무지팡이(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무활(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검(일반)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -676,30 +420,6 @@
     <t>ItemIcon_Gear_Armor</t>
   </si>
   <si>
-    <t>가죽 장갑</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑(일반)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑(매직)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑(레어)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑(에픽)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑(레전드)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>ItemIcon_Gear_Shield_Metal</t>
   </si>
   <si>
@@ -707,6 +427,435 @@
   </si>
   <si>
     <t>ItemIcon_Gear_Ring</t>
+  </si>
+  <si>
+    <t>StatOptionValue_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatOptionType_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillOption_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword2</t>
+  </si>
+  <si>
+    <t>Sword3</t>
+  </si>
+  <si>
+    <t>Sword4</t>
+  </si>
+  <si>
+    <t>Sword5</t>
+  </si>
+  <si>
+    <t>Bow1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow2</t>
+  </si>
+  <si>
+    <t>Bow3</t>
+  </si>
+  <si>
+    <t>Bow4</t>
+  </si>
+  <si>
+    <t>Bow5</t>
+  </si>
+  <si>
+    <t>Bow(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff2</t>
+  </si>
+  <si>
+    <t>Staff3</t>
+  </si>
+  <si>
+    <t>Staff4</t>
+  </si>
+  <si>
+    <t>Staff5</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Hammer</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet2</t>
+  </si>
+  <si>
+    <t>Helmet3</t>
+  </si>
+  <si>
+    <t>Helmet4</t>
+  </si>
+  <si>
+    <t>Helmet5</t>
+  </si>
+  <si>
+    <t>Armor1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor2</t>
+  </si>
+  <si>
+    <t>Armor3</t>
+  </si>
+  <si>
+    <t>Armor4</t>
+  </si>
+  <si>
+    <t>Armor5</t>
+  </si>
+  <si>
+    <t>Glove1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove2</t>
+  </si>
+  <si>
+    <t>Glove3</t>
+  </si>
+  <si>
+    <t>Glove4</t>
+  </si>
+  <si>
+    <t>Glove5</t>
+  </si>
+  <si>
+    <t>Shield1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield2</t>
+  </si>
+  <si>
+    <t>Shield3</t>
+  </si>
+  <si>
+    <t>Shield5</t>
+  </si>
+  <si>
+    <t>Boots1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots2</t>
+  </si>
+  <si>
+    <t>Boots3</t>
+  </si>
+  <si>
+    <t>Boots4</t>
+  </si>
+  <si>
+    <t>Boots5</t>
+  </si>
+  <si>
+    <t>Ring1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring2</t>
+  </si>
+  <si>
+    <t>Ring3</t>
+  </si>
+  <si>
+    <t>Ring4</t>
+  </si>
+  <si>
+    <t>Ring5</t>
+  </si>
+  <si>
+    <t>Amulet1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet2</t>
+  </si>
+  <si>
+    <t>Amulet3</t>
+  </si>
+  <si>
+    <t>Amulet4</t>
+  </si>
+  <si>
+    <t>Amulet5</t>
+  </si>
+  <si>
+    <t>Earring1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring2</t>
+  </si>
+  <si>
+    <t>Earring3</t>
+  </si>
+  <si>
+    <t>Earring4</t>
+  </si>
+  <si>
+    <t>Earring5</t>
+  </si>
+  <si>
+    <t>Helmet(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1241,7 +1390,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1263,58 +1412,58 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1409,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F1" s="13"/>
     </row>
@@ -1425,43 +1574,43 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1476,43 +1625,43 @@
         <v>5</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -1521,34 +1670,34 @@
         <v>100001</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1">
         <v>10001</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K4" s="7">
         <v>10</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M4" s="7">
         <v>0.1</v>
@@ -1564,34 +1713,34 @@
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1">
         <v>15</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M5" s="1">
         <v>0.2</v>
@@ -1602,34 +1751,34 @@
         <v>100003</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I6" s="1">
         <v>10001</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K6" s="1">
         <v>20</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M6" s="1">
         <v>0.3</v>
@@ -1640,34 +1789,34 @@
         <v>100004</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1">
         <v>10001</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1">
         <v>25</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="M7" s="1">
         <v>0.4</v>
@@ -1678,34 +1827,34 @@
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1">
         <v>10001</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1">
         <v>30</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M8" s="1">
         <v>0.5</v>
@@ -1717,34 +1866,34 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I9" s="1">
         <v>10002</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K9" s="7">
         <v>20</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M9" s="7">
         <v>5</v>
@@ -1760,34 +1909,34 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I10" s="1">
         <v>10002</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1">
         <v>25</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M10" s="1">
         <v>10</v>
@@ -1799,34 +1948,34 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I11" s="1">
         <v>10002</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1">
         <v>30</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M11" s="1">
         <v>15</v>
@@ -1840,31 +1989,31 @@
         <v>111</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I12" s="1">
         <v>10002</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1">
         <v>35</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M12" s="1">
         <v>20</v>
@@ -1875,34 +2024,34 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I13" s="1">
         <v>10002</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K13" s="1">
         <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M13" s="1">
         <v>25</v>
@@ -1914,34 +2063,34 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I14" s="1">
         <v>10003</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K14" s="7">
         <v>15</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M14" s="7">
         <v>-0.3</v>
@@ -1957,34 +2106,34 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I15" s="1">
         <v>10003</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K15" s="1">
         <v>20</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M15" s="1">
         <v>-0.2</v>
@@ -1995,34 +2144,34 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I16" s="1">
         <v>10003</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K16" s="1">
         <v>25</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M16" s="1">
         <v>-0.1</v>
@@ -2033,34 +2182,34 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I17" s="1">
         <v>10003</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1">
         <v>30</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M17" s="1">
         <v>0.1</v>
@@ -2072,34 +2221,34 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I18" s="1">
         <v>10003</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K18" s="1">
         <v>35</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M18" s="1">
         <v>0.2</v>
@@ -2112,25 +2261,25 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I19" s="1">
         <v>20001</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K19" s="1">
         <v>300</v>
@@ -2142,26 +2291,26 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="1">
         <v>20001</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K20" s="1">
         <v>500</v>
@@ -2173,25 +2322,25 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I21" s="1">
         <v>20001</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K21" s="1">
         <v>800</v>
@@ -2203,25 +2352,25 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I22" s="1">
         <v>20001</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K22" s="1">
         <v>1000</v>
@@ -2233,25 +2382,25 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1">
         <v>20001</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K23" s="1">
         <v>1500</v>
@@ -2264,25 +2413,25 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I24" s="1">
         <v>20002</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -2294,26 +2443,26 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="1">
         <v>20002</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1">
         <v>200</v>
@@ -2325,25 +2474,25 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I26" s="1">
         <v>20002</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1">
         <v>300</v>
@@ -2355,25 +2504,25 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I27" s="1">
         <v>20002</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1">
         <v>400</v>
@@ -2385,25 +2534,25 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I28" s="1">
         <v>20002</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K28" s="1">
         <v>500</v>
@@ -2416,25 +2565,25 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I29" s="1">
         <v>20003</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="K29" s="1">
         <v>0.02</v>
@@ -2446,26 +2595,26 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="1">
         <v>20003</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="K30" s="1">
         <v>0.04</v>
@@ -2477,25 +2626,25 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I31" s="1">
         <v>20003</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="K31" s="1">
         <v>0.06</v>
@@ -2507,25 +2656,25 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I32" s="1">
         <v>20003</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="K32" s="1">
         <v>0.08</v>
@@ -2537,25 +2686,25 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I33" s="1">
         <v>20003</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
@@ -2567,25 +2716,25 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I34" s="1">
         <v>20004</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="K34" s="1">
         <v>20</v>
@@ -2596,26 +2745,26 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="1">
         <v>20004</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="K35" s="1">
         <v>25</v>
@@ -2626,25 +2775,25 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I36" s="1">
         <v>20004</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -2655,25 +2804,25 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I37" s="1">
         <v>20004</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="K37" s="1">
         <v>40</v>
@@ -2684,25 +2833,25 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I38" s="1">
         <v>20004</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="K38" s="1">
         <v>50</v>
@@ -2714,25 +2863,25 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I39" s="1">
         <v>20005</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
@@ -2743,26 +2892,26 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="1">
         <v>20005</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2773,25 +2922,25 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I41" s="1">
         <v>20005</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="K41" s="1">
         <v>3</v>
@@ -2802,25 +2951,25 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I42" s="1">
         <v>20005</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="K42" s="1">
         <v>4</v>
@@ -2831,25 +2980,25 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I43" s="1">
         <v>20005</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="K43" s="1">
         <v>5</v>
@@ -2860,25 +3009,25 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I44" s="1">
         <v>30001</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -2889,25 +3038,25 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I45" s="1">
         <v>30001</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K45" s="1">
         <v>200</v>
@@ -2919,25 +3068,25 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I46" s="1">
         <v>30001</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K46" s="1">
         <v>300</v>
@@ -2949,25 +3098,25 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I47" s="1">
         <v>30001</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K47" s="1">
         <v>400</v>
@@ -2979,25 +3128,25 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I48" s="1">
         <v>30001</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K48" s="1">
         <v>500</v>
@@ -3009,25 +3158,25 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I49" s="1">
         <v>30002</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K49" s="1">
         <v>10</v>
@@ -3038,26 +3187,26 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="1">
         <v>30002</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K50" s="1">
         <v>20</v>
@@ -3068,26 +3217,26 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="1">
         <v>30002</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K51" s="1">
         <v>30</v>
@@ -3098,25 +3247,25 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I52" s="1">
         <v>30002</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K52" s="1">
         <v>40</v>
@@ -3127,25 +3276,25 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>88</v>
+        <v>202</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I53" s="1">
         <v>30002</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K53" s="1">
         <v>50</v>
@@ -3156,25 +3305,25 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I54" s="1">
         <v>30003</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="K54" s="1">
         <v>2.5</v>
@@ -3185,25 +3334,25 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>90</v>
+        <v>204</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I55" s="1">
         <v>30003</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="K55" s="1">
         <v>5</v>
@@ -3214,25 +3363,25 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I56" s="1">
         <v>30003</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="K56" s="1">
         <v>10</v>
@@ -3243,25 +3392,25 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I57" s="1">
         <v>30003</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="K57" s="1">
         <v>12</v>
@@ -3272,25 +3421,25 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I58" s="1">
         <v>30003</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="K58" s="1">
         <v>15</v>
@@ -3356,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3365,40 +3514,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3407,40 +3556,40 @@
         <v>4</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3452,7 +3601,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3467,7 +3616,7 @@
         <v>-0.02</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J4" s="7">
         <v>2</v>
@@ -3486,7 +3635,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3501,7 +3650,7 @@
         <v>-0.02</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -3520,7 +3669,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3535,7 +3684,7 @@
         <v>-0.02</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -3554,7 +3703,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3569,7 +3718,7 @@
         <v>-0.02</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -3588,7 +3737,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3603,7 +3752,7 @@
         <v>-0.02</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J8" s="7">
         <v>2</v>
@@ -3622,7 +3771,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3637,7 +3786,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3655,7 +3804,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3670,7 +3819,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3684,7 +3833,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3699,7 +3848,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3713,7 +3862,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3728,7 +3877,7 @@
         <v>-0.02</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
@@ -3742,7 +3891,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3757,7 +3906,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3771,7 +3920,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3786,7 +3935,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -3837,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -3851,37 +4000,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -3890,37 +4039,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="211">
   <si>
     <t>!Table</t>
   </si>
@@ -855,6 +855,18 @@
   </si>
   <si>
     <t>Earring(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitSlotValue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitSlotIndex</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1390,7 +1402,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1531,7 +1543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="11"/>
@@ -1553,7 +1565,7 @@
     <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1574,7 @@
       </c>
       <c r="F1" s="13"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
         <v>1</v>
@@ -1612,8 +1624,14 @@
       <c r="Q2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
         <v>4</v>
@@ -1663,8 +1681,14 @@
       <c r="Q3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="1">
         <v>100001</v>
@@ -1707,7 +1731,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="10"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="1">
         <v>100002</v>
@@ -1746,7 +1770,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>100003</v>
       </c>
@@ -1784,7 +1808,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>100004</v>
       </c>
@@ -1822,7 +1846,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>100005</v>
       </c>
@@ -1860,7 +1884,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="1">
         <v>100006</v>
@@ -1903,7 +1927,7 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="10"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="1">
         <v>100007</v>
@@ -1943,7 +1967,7 @@
       </c>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>100008</v>
       </c>
@@ -1981,7 +2005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>100009</v>
       </c>
@@ -2019,7 +2043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>100010</v>
       </c>
@@ -2057,7 +2081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="1">
         <v>100011</v>
@@ -2100,7 +2124,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="10"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="1">
         <v>100012</v>
@@ -2139,7 +2163,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>100013</v>
       </c>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -1402,7 +1402,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1807,6 +1807,12 @@
       <c r="M6" s="1">
         <v>0.3</v>
       </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" s="1">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -58,10 +58,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>StatOptionType_2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -867,6 +863,10 @@
   </si>
   <si>
     <t>TraitSlotIndex</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1402,7 +1402,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1424,58 +1424,58 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="13"/>
     </row>
@@ -1586,49 +1586,49 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1643,49 +1643,49 @@
         <v>5</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>7</v>
+        <v>210</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>7</v>
+        <v>210</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1694,34 +1694,34 @@
         <v>100001</v>
       </c>
       <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1">
         <v>10001</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" s="7">
         <v>10</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M4" s="7">
         <v>0.1</v>
@@ -1737,34 +1737,34 @@
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
         <v>15</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" s="1">
         <v>0.2</v>
@@ -1775,34 +1775,34 @@
         <v>100003</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I6" s="1">
         <v>10001</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" s="1">
         <v>20</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M6" s="1">
         <v>0.3</v>
@@ -1819,34 +1819,34 @@
         <v>100004</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="1">
         <v>10001</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" s="1">
         <v>25</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7" s="1">
         <v>0.4</v>
@@ -1857,34 +1857,34 @@
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" s="1">
         <v>10001</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
         <v>30</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M8" s="1">
         <v>0.5</v>
@@ -1896,34 +1896,34 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1">
         <v>10002</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" s="7">
         <v>20</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M9" s="7">
         <v>5</v>
@@ -1939,34 +1939,34 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1">
         <v>10002</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1">
         <v>25</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M10" s="1">
         <v>10</v>
@@ -1978,34 +1978,34 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11" s="1">
         <v>10002</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" s="1">
         <v>30</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M11" s="1">
         <v>15</v>
@@ -2016,34 +2016,34 @@
         <v>100009</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I12" s="1">
         <v>10002</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K12" s="1">
         <v>35</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M12" s="1">
         <v>20</v>
@@ -2054,34 +2054,34 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1">
         <v>10002</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K13" s="1">
         <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M13" s="1">
         <v>25</v>
@@ -2093,34 +2093,34 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" s="1">
         <v>10003</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K14" s="7">
         <v>15</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M14" s="7">
         <v>-0.3</v>
@@ -2136,34 +2136,34 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" s="1">
         <v>10003</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K15" s="1">
         <v>20</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M15" s="1">
         <v>-0.2</v>
@@ -2174,34 +2174,34 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="1">
         <v>10003</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K16" s="1">
         <v>25</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M16" s="1">
         <v>-0.1</v>
@@ -2212,34 +2212,34 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" s="1">
         <v>10003</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K17" s="1">
         <v>30</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M17" s="1">
         <v>0.1</v>
@@ -2251,34 +2251,34 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18" s="1">
         <v>10003</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K18" s="1">
         <v>35</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M18" s="1">
         <v>0.2</v>
@@ -2291,25 +2291,25 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I19" s="1">
         <v>20001</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K19" s="1">
         <v>300</v>
@@ -2321,26 +2321,26 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="1">
         <v>20001</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K20" s="1">
         <v>500</v>
@@ -2352,25 +2352,25 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="1">
         <v>20001</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K21" s="1">
         <v>800</v>
@@ -2382,25 +2382,25 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I22" s="1">
         <v>20001</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K22" s="1">
         <v>1000</v>
@@ -2412,25 +2412,25 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I23" s="1">
         <v>20001</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K23" s="1">
         <v>1500</v>
@@ -2443,25 +2443,25 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I24" s="1">
         <v>20002</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -2473,26 +2473,26 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="1">
         <v>20002</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K25" s="1">
         <v>200</v>
@@ -2504,25 +2504,25 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I26" s="1">
         <v>20002</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K26" s="1">
         <v>300</v>
@@ -2534,25 +2534,25 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I27" s="1">
         <v>20002</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1">
         <v>400</v>
@@ -2564,25 +2564,25 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="1">
         <v>20002</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K28" s="1">
         <v>500</v>
@@ -2595,25 +2595,25 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I29" s="1">
         <v>20003</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K29" s="1">
         <v>0.02</v>
@@ -2625,26 +2625,26 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="1">
         <v>20003</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K30" s="1">
         <v>0.04</v>
@@ -2656,25 +2656,25 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I31" s="1">
         <v>20003</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K31" s="1">
         <v>0.06</v>
@@ -2686,25 +2686,25 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I32" s="1">
         <v>20003</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K32" s="1">
         <v>0.08</v>
@@ -2716,25 +2716,25 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I33" s="1">
         <v>20003</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
@@ -2746,25 +2746,25 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I34" s="1">
         <v>20004</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K34" s="1">
         <v>20</v>
@@ -2775,26 +2775,26 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="1">
         <v>20004</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K35" s="1">
         <v>25</v>
@@ -2805,25 +2805,25 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I36" s="1">
         <v>20004</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -2834,25 +2834,25 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1">
         <v>20004</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K37" s="1">
         <v>40</v>
@@ -2863,25 +2863,25 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I38" s="1">
         <v>20004</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K38" s="1">
         <v>50</v>
@@ -2893,25 +2893,25 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I39" s="1">
         <v>20005</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
@@ -2922,26 +2922,26 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="1">
         <v>20005</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2952,25 +2952,25 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I41" s="1">
         <v>20005</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K41" s="1">
         <v>3</v>
@@ -2981,25 +2981,25 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I42" s="1">
         <v>20005</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K42" s="1">
         <v>4</v>
@@ -3010,25 +3010,25 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I43" s="1">
         <v>20005</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K43" s="1">
         <v>5</v>
@@ -3039,25 +3039,25 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I44" s="1">
         <v>30001</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -3068,25 +3068,25 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I45" s="1">
         <v>30001</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K45" s="1">
         <v>200</v>
@@ -3098,25 +3098,25 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I46" s="1">
         <v>30001</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K46" s="1">
         <v>300</v>
@@ -3128,25 +3128,25 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I47" s="1">
         <v>30001</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K47" s="1">
         <v>400</v>
@@ -3158,25 +3158,25 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I48" s="1">
         <v>30001</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K48" s="1">
         <v>500</v>
@@ -3188,25 +3188,25 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I49" s="1">
         <v>30002</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K49" s="1">
         <v>10</v>
@@ -3217,26 +3217,26 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="1">
         <v>30002</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K50" s="1">
         <v>20</v>
@@ -3247,26 +3247,26 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="1">
         <v>30002</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K51" s="1">
         <v>30</v>
@@ -3277,25 +3277,25 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I52" s="1">
         <v>30002</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K52" s="1">
         <v>40</v>
@@ -3306,25 +3306,25 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I53" s="1">
         <v>30002</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K53" s="1">
         <v>50</v>
@@ -3335,25 +3335,25 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I54" s="1">
         <v>30003</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K54" s="1">
         <v>2.5</v>
@@ -3364,25 +3364,25 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I55" s="1">
         <v>30003</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K55" s="1">
         <v>5</v>
@@ -3393,25 +3393,25 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I56" s="1">
         <v>30003</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K56" s="1">
         <v>10</v>
@@ -3422,25 +3422,25 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I57" s="1">
         <v>30003</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K57" s="1">
         <v>12</v>
@@ -3451,25 +3451,25 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I58" s="1">
         <v>30003</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K58" s="1">
         <v>15</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3544,40 +3544,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="H2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3586,40 +3586,40 @@
         <v>4</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>55</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3631,7 +3631,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3646,7 +3646,7 @@
         <v>-0.02</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" s="7">
         <v>2</v>
@@ -3665,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3680,7 +3680,7 @@
         <v>-0.02</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -3699,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3714,7 +3714,7 @@
         <v>-0.02</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -3733,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3748,7 +3748,7 @@
         <v>-0.02</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -3767,7 +3767,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3782,7 +3782,7 @@
         <v>-0.02</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" s="7">
         <v>2</v>
@@ -3801,7 +3801,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3816,7 +3816,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3834,7 +3834,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3849,7 +3849,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3863,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3878,7 +3878,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3892,7 +3892,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3907,7 +3907,7 @@
         <v>-0.02</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
@@ -3921,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3936,7 +3936,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3950,7 +3950,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3965,7 +3965,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -4016,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -4030,37 +4030,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="H2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -4069,37 +4069,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -295,10 +295,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>StepStatOptionType_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>StepStatOptionType_2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -867,6 +863,10 @@
   </si>
   <si>
     <t>!SkillInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StepStatOptionType_1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1427,7 +1427,7 @@
         <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1450,7 +1450,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1592,7 +1592,7 @@
         <v>19</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>37</v>
@@ -1601,10 +1601,10 @@
         <v>56</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>7</v>
@@ -1619,16 +1619,16 @@
         <v>30</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1649,7 +1649,7 @@
         <v>45</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>33</v>
@@ -1676,16 +1676,16 @@
         <v>43</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1694,13 +1694,13 @@
         <v>100001</v>
       </c>
       <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>16</v>
@@ -1737,19 +1737,19 @@
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>34</v>
@@ -1775,19 +1775,19 @@
         <v>100003</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>34</v>
@@ -1819,19 +1819,19 @@
         <v>100004</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>34</v>
@@ -1857,19 +1857,19 @@
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>34</v>
@@ -1896,13 +1896,13 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>16</v>
@@ -1939,13 +1939,13 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>16</v>
@@ -1978,13 +1978,13 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>16</v>
@@ -2016,13 +2016,13 @@
         <v>100009</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
@@ -2054,13 +2054,13 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>16</v>
@@ -2093,13 +2093,13 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>16</v>
@@ -2136,13 +2136,13 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>16</v>
@@ -2174,13 +2174,13 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>16</v>
@@ -2212,13 +2212,13 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>16</v>
@@ -2251,13 +2251,13 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>16</v>
@@ -2291,13 +2291,13 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>17</v>
@@ -2321,13 +2321,13 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>17</v>
@@ -2352,13 +2352,13 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>17</v>
@@ -2382,13 +2382,13 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>17</v>
@@ -2412,13 +2412,13 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>17</v>
@@ -2443,13 +2443,13 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>17</v>
@@ -2473,13 +2473,13 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>17</v>
@@ -2504,13 +2504,13 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>17</v>
@@ -2534,13 +2534,13 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>17</v>
@@ -2564,13 +2564,13 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>17</v>
@@ -2595,13 +2595,13 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
@@ -2625,13 +2625,13 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>17</v>
@@ -2656,13 +2656,13 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>17</v>
@@ -2686,13 +2686,13 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>17</v>
@@ -2716,13 +2716,13 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>17</v>
@@ -2746,13 +2746,13 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>17</v>
@@ -2775,13 +2775,13 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>17</v>
@@ -2805,13 +2805,13 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>17</v>
@@ -2834,13 +2834,13 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>17</v>
@@ -2863,13 +2863,13 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>17</v>
@@ -2893,13 +2893,13 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>17</v>
@@ -2922,13 +2922,13 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>17</v>
@@ -2952,13 +2952,13 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>17</v>
@@ -2981,13 +2981,13 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>17</v>
@@ -3010,13 +3010,13 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>17</v>
@@ -3039,13 +3039,13 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>18</v>
@@ -3068,13 +3068,13 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>18</v>
@@ -3098,13 +3098,13 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>18</v>
@@ -3128,13 +3128,13 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
@@ -3158,13 +3158,13 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>18</v>
@@ -3188,13 +3188,13 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>18</v>
@@ -3217,13 +3217,13 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>18</v>
@@ -3247,13 +3247,13 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>18</v>
@@ -3277,13 +3277,13 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>18</v>
@@ -3306,13 +3306,13 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>18</v>
@@ -3335,13 +3335,13 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>18</v>
@@ -3364,13 +3364,13 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>18</v>
@@ -3393,13 +3393,13 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>18</v>
@@ -3422,13 +3422,13 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>18</v>
@@ -3451,13 +3451,13 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>18</v>
@@ -3544,40 +3544,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="H2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3589,7 +3589,7 @@
         <v>46</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>54</v>
@@ -3619,7 +3619,7 @@
         <v>54</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3631,7 +3631,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3665,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3699,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3733,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3767,7 +3767,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3801,7 +3801,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3834,7 +3834,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3863,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3892,7 +3892,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3921,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3950,7 +3950,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -4030,19 +4030,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>49</v>
@@ -4072,13 +4072,13 @@
         <v>54</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>54</v>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="207">
   <si>
     <t>!Table</t>
   </si>
@@ -186,26 +186,6 @@
     <t>CritRate_Add</t>
   </si>
   <si>
-    <t>!CharacterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Melee</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Ranged</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Mage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BindCharacter</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>AtkSpeed_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -384,489 +364,493 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>!ItemGradeTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipmentTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Sword</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Bow</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Hammer</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Helmet</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Armor</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Shield_Metal</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Ring</t>
+  </si>
+  <si>
+    <t>StatOptionValue_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatOptionType_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillOption_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword2</t>
+  </si>
+  <si>
+    <t>Sword3</t>
+  </si>
+  <si>
+    <t>Sword4</t>
+  </si>
+  <si>
+    <t>Sword5</t>
+  </si>
+  <si>
+    <t>Bow1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow2</t>
+  </si>
+  <si>
+    <t>Bow3</t>
+  </si>
+  <si>
+    <t>Bow4</t>
+  </si>
+  <si>
+    <t>Bow5</t>
+  </si>
+  <si>
+    <t>Bow(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff2</t>
+  </si>
+  <si>
+    <t>Staff3</t>
+  </si>
+  <si>
+    <t>Staff4</t>
+  </si>
+  <si>
+    <t>Staff5</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gear_Hammer</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staff(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet2</t>
+  </si>
+  <si>
+    <t>Helmet3</t>
+  </si>
+  <si>
+    <t>Helmet4</t>
+  </si>
+  <si>
+    <t>Helmet5</t>
+  </si>
+  <si>
+    <t>Armor1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor2</t>
+  </si>
+  <si>
+    <t>Armor3</t>
+  </si>
+  <si>
+    <t>Armor4</t>
+  </si>
+  <si>
+    <t>Armor5</t>
+  </si>
+  <si>
+    <t>Glove1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove2</t>
+  </si>
+  <si>
+    <t>Glove3</t>
+  </si>
+  <si>
+    <t>Glove4</t>
+  </si>
+  <si>
+    <t>Glove5</t>
+  </si>
+  <si>
+    <t>Shield1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield2</t>
+  </si>
+  <si>
+    <t>Shield3</t>
+  </si>
+  <si>
+    <t>Shield5</t>
+  </si>
+  <si>
+    <t>Boots1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots2</t>
+  </si>
+  <si>
+    <t>Boots3</t>
+  </si>
+  <si>
+    <t>Boots4</t>
+  </si>
+  <si>
+    <t>Boots5</t>
+  </si>
+  <si>
+    <t>Ring1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring2</t>
+  </si>
+  <si>
+    <t>Ring3</t>
+  </si>
+  <si>
+    <t>Ring4</t>
+  </si>
+  <si>
+    <t>Ring5</t>
+  </si>
+  <si>
+    <t>Amulet1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet2</t>
+  </si>
+  <si>
+    <t>Amulet3</t>
+  </si>
+  <si>
+    <t>Amulet4</t>
+  </si>
+  <si>
+    <t>Amulet5</t>
+  </si>
+  <si>
+    <t>Earring1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring2</t>
+  </si>
+  <si>
+    <t>Earring3</t>
+  </si>
+  <si>
+    <t>Earring4</t>
+  </si>
+  <si>
+    <t>Earring5</t>
+  </si>
+  <si>
+    <t>Helmet(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glove(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Normal)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Magic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Rare)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Epic)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earring(Legendary)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitSlotValue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitSlotIndex</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StepStatOptionType_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>ItemGradeTypes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>!ItemGradeTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EquipmentTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Sword</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Bow</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Hammer</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Helmet</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Armor</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Shield_Metal</t>
-  </si>
-  <si>
-    <t>ItemIcon_Energy_Blue</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Ring</t>
-  </si>
-  <si>
-    <t>StatOptionValue_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatOptionType_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillOption_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Epic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sword2</t>
-  </si>
-  <si>
-    <t>Sword3</t>
-  </si>
-  <si>
-    <t>Sword4</t>
-  </si>
-  <si>
-    <t>Sword5</t>
-  </si>
-  <si>
-    <t>Bow1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bow(normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bow2</t>
-  </si>
-  <si>
-    <t>Bow3</t>
-  </si>
-  <si>
-    <t>Bow4</t>
-  </si>
-  <si>
-    <t>Bow5</t>
-  </si>
-  <si>
-    <t>Bow(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bow(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bow(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bow(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff2</t>
-  </si>
-  <si>
-    <t>Staff3</t>
-  </si>
-  <si>
-    <t>Staff4</t>
-  </si>
-  <si>
-    <t>Staff5</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Hammer</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Staff(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Helmet1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Helmet2</t>
-  </si>
-  <si>
-    <t>Helmet3</t>
-  </si>
-  <si>
-    <t>Helmet4</t>
-  </si>
-  <si>
-    <t>Helmet5</t>
-  </si>
-  <si>
-    <t>Armor1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor2</t>
-  </si>
-  <si>
-    <t>Armor3</t>
-  </si>
-  <si>
-    <t>Armor4</t>
-  </si>
-  <si>
-    <t>Armor5</t>
-  </si>
-  <si>
-    <t>Glove1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glove2</t>
-  </si>
-  <si>
-    <t>Glove3</t>
-  </si>
-  <si>
-    <t>Glove4</t>
-  </si>
-  <si>
-    <t>Glove5</t>
-  </si>
-  <si>
-    <t>Shield1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield2</t>
-  </si>
-  <si>
-    <t>Shield3</t>
-  </si>
-  <si>
-    <t>Shield5</t>
-  </si>
-  <si>
-    <t>Boots1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boots2</t>
-  </si>
-  <si>
-    <t>Boots3</t>
-  </si>
-  <si>
-    <t>Boots4</t>
-  </si>
-  <si>
-    <t>Boots5</t>
-  </si>
-  <si>
-    <t>Ring1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ring2</t>
-  </si>
-  <si>
-    <t>Ring3</t>
-  </si>
-  <si>
-    <t>Ring4</t>
-  </si>
-  <si>
-    <t>Ring5</t>
-  </si>
-  <si>
-    <t>Amulet1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amulet2</t>
-  </si>
-  <si>
-    <t>Amulet3</t>
-  </si>
-  <si>
-    <t>Amulet4</t>
-  </si>
-  <si>
-    <t>Amulet5</t>
-  </si>
-  <si>
-    <t>Earring1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earring2</t>
-  </si>
-  <si>
-    <t>Earring3</t>
-  </si>
-  <si>
-    <t>Earring4</t>
-  </si>
-  <si>
-    <t>Earring5</t>
-  </si>
-  <si>
-    <t>Helmet(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Helmet(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Helmet(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Helmet(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Helmet(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glove(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glove(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glove(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glove(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Glove(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield(normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shield(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boots(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boots(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boots(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boots(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boots(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ring(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ring(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ring(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ring(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ring(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amulet(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amulet(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amulet(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amulet(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amulet(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earring(Normal)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earring(Magic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earring(Rare)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earring(Epic)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earring(Legendary)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TraitSlotValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TraitSlotIndex</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StepStatOptionType_1</t>
+    <t>ATK_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -874,7 +858,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -941,14 +925,6 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -1064,12 +1040,12 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1087,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -1096,12 +1072,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1402,7 +1375,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1427,7 +1400,7 @@
         <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1450,90 +1423,90 @@
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>77</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B12" s="16"/>
+      <c r="B12" s="15"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B13" s="16"/>
+      <c r="B13" s="15"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B14" s="16"/>
+      <c r="B14" s="15"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B15" s="16"/>
+      <c r="B15" s="15"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B16" s="16"/>
+      <c r="B16" s="15"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="16"/>
+      <c r="B17" s="15"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="16"/>
+      <c r="B18" s="15"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="16"/>
+      <c r="B19" s="15"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="16"/>
+      <c r="B20" s="15"/>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="16"/>
+      <c r="B21" s="15"/>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" s="16"/>
+      <c r="B22" s="15"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" s="16"/>
+      <c r="B23" s="15"/>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="16"/>
+      <c r="B24" s="15"/>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" s="16"/>
+      <c r="B25" s="15"/>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" s="16"/>
+      <c r="B26" s="15"/>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" s="16"/>
+      <c r="B27" s="15"/>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="16"/>
+      <c r="B28" s="15"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" s="16"/>
+      <c r="B30" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -1543,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="11"/>
@@ -1553,28 +1526,27 @@
     <col min="5" max="5" width="26.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="18.125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="15.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="18.125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
         <v>1</v>
@@ -1585,53 +1557,50 @@
       <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>56</v>
+      <c r="G2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
         <v>4</v>
@@ -1642,1865 +1611,1810 @@
       <c r="D3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>78</v>
+        <v>40</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="L3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>43</v>
+        <v>203</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="1">
         <v>100001</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="H4" s="1">
         <v>10001</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="7">
+      <c r="J4" s="7">
         <v>10</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="7">
+      <c r="L4" s="7">
         <v>0.1</v>
       </c>
+      <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="10"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="1">
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="G5" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="1">
         <v>10001</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="1">
+      <c r="J5" s="1">
         <v>15</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="1">
+      <c r="L5" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>100003</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="G6" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="1">
         <v>10001</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="1">
+      <c r="J6" s="1">
         <v>20</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="1">
+      <c r="L6" s="1">
         <v>0.3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <v>1</v>
       </c>
-      <c r="S6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>100004</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="G7" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="1">
         <v>10001</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="1">
+      <c r="J7" s="1">
         <v>25</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="K7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="G8" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="1">
         <v>10001</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="1">
+      <c r="J8" s="1">
         <v>30</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="1">
+      <c r="L8" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="1">
         <v>100006</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="H9" s="1">
         <v>10002</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="7">
+      <c r="J9" s="7">
         <v>20</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="7">
+      <c r="L9" s="7">
         <v>5</v>
       </c>
+      <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="10"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="1">
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="H10" s="1">
         <v>10002</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="1">
+      <c r="J10" s="1">
         <v>25</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="1">
+      <c r="L10" s="1">
         <v>10</v>
       </c>
-      <c r="O10" s="7"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="H11" s="1">
         <v>10002</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K11" s="1">
+      <c r="J11" s="1">
         <v>30</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="1">
+      <c r="L11" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>100009</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="1">
+        <v>10002</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
         <v>35</v>
       </c>
-      <c r="I12" s="1">
-        <v>10002</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="1">
-        <v>35</v>
-      </c>
-      <c r="L12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="1">
+      <c r="L12" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="H13" s="1">
         <v>10002</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="1">
+      <c r="J13" s="1">
         <v>40</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M13" s="1">
+      <c r="L13" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="1">
         <v>100011</v>
       </c>
       <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="H14" s="1">
         <v>10003</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K14" s="7">
+      <c r="J14" s="7">
         <v>15</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="7">
+      <c r="L14" s="7">
         <v>-0.3</v>
       </c>
+      <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="10"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="1">
         <v>100012</v>
       </c>
       <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="1">
+      <c r="H15" s="1">
         <v>10003</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="1">
+      <c r="J15" s="1">
         <v>20</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="1">
+      <c r="L15" s="1">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>100013</v>
       </c>
       <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="1">
+      <c r="H16" s="1">
         <v>10003</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K16" s="1">
+      <c r="J16" s="1">
         <v>25</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="1">
+      <c r="L16" s="1">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>100014</v>
       </c>
       <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="1">
+      <c r="H17" s="1">
         <v>10003</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="1">
+      <c r="J17" s="1">
         <v>30</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="1">
+      <c r="L17" s="1">
         <v>0.1</v>
       </c>
-      <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>100015</v>
       </c>
       <c r="C18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="1">
+      <c r="H18" s="1">
         <v>10003</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="1">
+      <c r="J18" s="1">
         <v>35</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="1">
+      <c r="L18" s="1">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="1">
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="1">
+      <c r="H19" s="1">
         <v>20001</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="1">
+      <c r="J19" s="1">
         <v>300</v>
       </c>
-      <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="1">
+      <c r="H20" s="1">
         <v>20001</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="1">
+      <c r="J20" s="1">
         <v>500</v>
       </c>
-      <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="1">
+      <c r="H21" s="1">
         <v>20001</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="1">
+      <c r="J21" s="1">
         <v>800</v>
       </c>
-      <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="1">
+      <c r="H22" s="1">
         <v>20001</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="1">
+      <c r="J22" s="1">
         <v>1000</v>
       </c>
-      <c r="Q22" s="1"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="1">
+      <c r="H23" s="1">
         <v>20001</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="1">
+      <c r="J23" s="1">
         <v>1500</v>
       </c>
-      <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="1">
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="1">
+      <c r="H24" s="1">
         <v>20002</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="1">
+      <c r="J24" s="1">
         <v>100</v>
       </c>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="1">
+      <c r="H25" s="1">
         <v>20002</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K25" s="1">
+      <c r="J25" s="1">
         <v>200</v>
       </c>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="1">
+      <c r="H26" s="1">
         <v>20002</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K26" s="1">
+      <c r="J26" s="1">
         <v>300</v>
       </c>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="1">
+      <c r="H27" s="1">
         <v>20002</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K27" s="1">
+      <c r="J27" s="1">
         <v>400</v>
       </c>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I28" s="1">
+      <c r="H28" s="1">
         <v>20002</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K28" s="1">
+      <c r="J28" s="1">
         <v>500</v>
       </c>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="1">
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="1">
+      <c r="H29" s="1">
         <v>20003</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="I29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="1">
         <v>0.02</v>
       </c>
-      <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="1">
+      <c r="H30" s="1">
         <v>20003</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="I30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="1">
         <v>0.04</v>
       </c>
-      <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B31" s="1">
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="1">
+      <c r="H31" s="1">
         <v>20003</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="I31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J31" s="1">
         <v>0.06</v>
       </c>
-      <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I32" s="1">
+      <c r="H32" s="1">
         <v>20003</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="I32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="1">
         <v>0.08</v>
       </c>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B33" s="1">
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I33" s="1">
+      <c r="H33" s="1">
         <v>20003</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="I33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="1">
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="1">
+      <c r="H34" s="1">
         <v>20004</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="I34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="1">
+      <c r="H35" s="1">
         <v>20004</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K35" s="1">
+      <c r="I35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>200018</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I36" s="1">
+      <c r="H36" s="1">
         <v>20004</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K36" s="1">
+      <c r="I36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B37" s="1">
         <v>200019</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="1">
+      <c r="H37" s="1">
         <v>20004</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K37" s="1">
+      <c r="I37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B38" s="1">
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="1">
+      <c r="H38" s="1">
         <v>20004</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K38" s="1">
+      <c r="I38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="1">
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I39" s="1">
+      <c r="H39" s="1">
         <v>20005</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="1">
+      <c r="I39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="1">
+      <c r="H40" s="1">
         <v>20005</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K40" s="1">
+      <c r="I40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J40" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
         <v>200023</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="1">
+      <c r="H41" s="1">
         <v>20005</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K41" s="1">
+      <c r="I41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J41" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G42" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I42" s="1">
+      <c r="H42" s="1">
         <v>20005</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K42" s="1">
+      <c r="I42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J42" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B43" s="1">
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I43" s="1">
+      <c r="H43" s="1">
         <v>20005</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K43" s="1">
+      <c r="I43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J43" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G44" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="1">
+      <c r="H44" s="1">
         <v>30001</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I44" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J44" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="1">
+      <c r="H45" s="1">
         <v>30001</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K45" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I45" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J45" s="1">
+        <v>6</v>
+      </c>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
         <v>300003</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I46" s="1">
+      <c r="H46" s="1">
         <v>30001</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K46" s="1">
-        <v>300</v>
-      </c>
-      <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I46" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J46" s="1">
+        <v>7</v>
+      </c>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="G47" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I47" s="1">
+      <c r="H47" s="1">
         <v>30001</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K47" s="1">
-        <v>400</v>
-      </c>
-      <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I47" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J47" s="1">
+        <v>8</v>
+      </c>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G48" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="1">
+      <c r="H48" s="1">
         <v>30001</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K48" s="1">
-        <v>500</v>
-      </c>
-      <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="I48" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J48" s="1">
+        <v>10</v>
+      </c>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="1">
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="G49" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I49" s="1">
+      <c r="H49" s="1">
         <v>30002</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K49" s="1">
+      <c r="I49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="16" t="s">
+      <c r="G50" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H50" s="8"/>
-      <c r="I50" s="1">
+      <c r="H50" s="1">
         <v>30002</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K50" s="1">
+      <c r="I50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="1">
+      <c r="H51" s="1">
         <v>30002</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K51" s="1">
+      <c r="I51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I52" s="1">
+      <c r="H52" s="1">
         <v>30002</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K52" s="1">
+      <c r="I52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J52" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="1">
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I53" s="1">
+      <c r="H53" s="1">
         <v>30002</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K53" s="1">
+      <c r="I53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J53" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="1">
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G54" s="16" t="s">
+      <c r="G54" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I54" s="1">
+      <c r="H54" s="1">
         <v>30003</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K54" s="1">
+      <c r="I54" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J54" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="1">
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G55" s="16" t="s">
+      <c r="G55" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="1">
+      <c r="H55" s="1">
         <v>30003</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K55" s="1">
+      <c r="I55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J55" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I56" s="1">
+      <c r="H56" s="1">
         <v>30003</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K56" s="1">
+      <c r="I56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I57" s="1">
+      <c r="H57" s="1">
         <v>30003</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K57" s="1">
+      <c r="I57" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J57" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="1">
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="G58" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I58" s="1">
+      <c r="H58" s="1">
         <v>30003</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K58" s="1">
+      <c r="I58" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J58" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="F59" s="16"/>
-      <c r="Q59" s="1"/>
-    </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="F59" s="15"/>
+      <c r="P59" s="1"/>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="F60"/>
-      <c r="Q60" s="1"/>
-    </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="P60" s="1"/>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="F61"/>
-      <c r="Q61" s="1"/>
-    </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="F62" s="16"/>
-      <c r="Q62" s="1"/>
-    </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="P61" s="1"/>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="F62" s="15"/>
+      <c r="P62" s="1"/>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="F63"/>
-      <c r="Q63" s="1"/>
-    </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="P63" s="1"/>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="F64"/>
-      <c r="Q64" s="1"/>
-    </row>
-    <row r="65" spans="17:17" x14ac:dyDescent="0.3">
-      <c r="Q65" s="1"/>
+      <c r="P64" s="1"/>
+    </row>
+    <row r="65" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P65" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3534,8 +3448,8 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>55</v>
+      <c r="B1" s="16" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3543,41 +3457,41 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="15" t="s">
+      <c r="N2" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3585,41 +3499,41 @@
       <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>57</v>
+      <c r="C3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3631,7 +3545,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3665,7 +3579,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3699,7 +3613,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3733,7 +3647,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3767,7 +3681,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3801,7 +3715,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3816,7 +3730,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3834,7 +3748,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3849,7 +3763,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3863,7 +3777,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3878,7 +3792,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3892,7 +3806,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3921,7 +3835,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3936,7 +3850,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3950,7 +3864,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3965,7 +3879,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -4015,14 +3929,14 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -4030,37 +3944,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -4069,37 +3983,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="206">
   <si>
     <t>!Table</t>
   </si>
@@ -84,9 +84,6 @@
   <si>
     <t>MaxHP_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
   </si>
   <si>
     <t>!Enum</t>
@@ -1375,7 +1372,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1397,58 +1394,58 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1542,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" s="12"/>
     </row>
@@ -1558,22 +1555,22 @@
         <v>3</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>7</v>
@@ -1582,22 +1579,22 @@
         <v>8</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -1612,46 +1609,46 @@
         <v>5</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -1660,19 +1657,19 @@
         <v>100001</v>
       </c>
       <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1">
         <v>10001</v>
@@ -1700,19 +1697,19 @@
         <v>100002</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" s="1">
         <v>10001</v>
@@ -1735,19 +1732,19 @@
         <v>100003</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" s="1">
         <v>10001</v>
@@ -1776,19 +1773,19 @@
         <v>100004</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" s="1">
         <v>10001</v>
@@ -1800,7 +1797,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="1">
         <v>0.4</v>
@@ -1811,19 +1808,19 @@
         <v>100005</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H8" s="1">
         <v>10001</v>
@@ -1847,19 +1844,19 @@
         <v>100006</v>
       </c>
       <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="1">
         <v>10002</v>
@@ -1871,7 +1868,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="7">
         <v>5</v>
@@ -1887,19 +1884,19 @@
         <v>100007</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" s="1">
         <v>10002</v>
@@ -1911,7 +1908,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L10" s="1">
         <v>10</v>
@@ -1923,19 +1920,19 @@
         <v>100008</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1">
         <v>10002</v>
@@ -1947,7 +1944,7 @@
         <v>30</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L11" s="1">
         <v>15</v>
@@ -1958,19 +1955,19 @@
         <v>100009</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="1">
         <v>10002</v>
@@ -1982,7 +1979,7 @@
         <v>35</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" s="1">
         <v>20</v>
@@ -1993,19 +1990,19 @@
         <v>100010</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="1">
         <v>10002</v>
@@ -2017,7 +2014,7 @@
         <v>40</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L13" s="1">
         <v>25</v>
@@ -2029,25 +2026,25 @@
         <v>100011</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" s="1">
         <v>10003</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J14" s="7">
         <v>15</v>
@@ -2069,25 +2066,25 @@
         <v>100012</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H15" s="1">
         <v>10003</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J15" s="1">
         <v>20</v>
@@ -2104,25 +2101,25 @@
         <v>100013</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H16" s="1">
         <v>10003</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J16" s="1">
         <v>25</v>
@@ -2139,25 +2136,25 @@
         <v>100014</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="1">
         <v>10003</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J17" s="1">
         <v>30</v>
@@ -2175,25 +2172,25 @@
         <v>100015</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" s="1">
         <v>10003</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J18" s="1">
         <v>35</v>
@@ -2212,19 +2209,19 @@
         <v>200001</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H19" s="1">
         <v>20001</v>
@@ -2242,19 +2239,19 @@
         <v>200002</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="1">
         <v>20001</v>
@@ -2272,19 +2269,19 @@
         <v>200003</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" s="1">
         <v>20001</v>
@@ -2302,19 +2299,19 @@
         <v>200004</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" s="1">
         <v>20001</v>
@@ -2332,19 +2329,19 @@
         <v>200005</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H23" s="1">
         <v>20001</v>
@@ -2363,19 +2360,19 @@
         <v>200006</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H24" s="1">
         <v>20002</v>
@@ -2393,19 +2390,19 @@
         <v>200007</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="1">
         <v>20002</v>
@@ -2423,19 +2420,19 @@
         <v>200008</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="1">
         <v>20002</v>
@@ -2453,19 +2450,19 @@
         <v>200009</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" s="1">
         <v>20002</v>
@@ -2483,19 +2480,19 @@
         <v>200010</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" s="1">
         <v>20002</v>
@@ -2514,25 +2511,25 @@
         <v>200011</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H29" s="1">
         <v>20003</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J29" s="1">
         <v>0.02</v>
@@ -2544,25 +2541,25 @@
         <v>200012</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="1">
         <v>20003</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" s="1">
         <v>0.04</v>
@@ -2574,25 +2571,25 @@
         <v>200013</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H31" s="1">
         <v>20003</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" s="1">
         <v>0.06</v>
@@ -2604,25 +2601,25 @@
         <v>200014</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H32" s="1">
         <v>20003</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J32" s="1">
         <v>0.08</v>
@@ -2634,25 +2631,25 @@
         <v>200015</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H33" s="1">
         <v>20003</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J33" s="1">
         <v>0.1</v>
@@ -2664,25 +2661,25 @@
         <v>200016</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H34" s="1">
         <v>20004</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J34" s="1">
         <v>20</v>
@@ -2693,25 +2690,25 @@
         <v>200017</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="1">
         <v>20004</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J35" s="1">
         <v>25</v>
@@ -2722,25 +2719,25 @@
         <v>200018</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H36" s="1">
         <v>20004</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J36" s="1">
         <v>30</v>
@@ -2751,25 +2748,25 @@
         <v>200019</v>
       </c>
       <c r="C37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" s="1">
         <v>20004</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J37" s="1">
         <v>40</v>
@@ -2780,25 +2777,25 @@
         <v>200020</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H38" s="1">
         <v>20004</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J38" s="1">
         <v>50</v>
@@ -2810,25 +2807,25 @@
         <v>200021</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H39" s="1">
         <v>20005</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J39" s="1">
         <v>1</v>
@@ -2839,25 +2836,25 @@
         <v>200022</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="1">
         <v>20005</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J40" s="1">
         <v>2</v>
@@ -2868,25 +2865,25 @@
         <v>200023</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H41" s="1">
         <v>20005</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J41" s="1">
         <v>3</v>
@@ -2897,25 +2894,25 @@
         <v>200024</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H42" s="1">
         <v>20005</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J42" s="1">
         <v>4</v>
@@ -2926,25 +2923,25 @@
         <v>200025</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H43" s="1">
         <v>20005</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J43" s="1">
         <v>5</v>
@@ -2955,25 +2952,25 @@
         <v>300001</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H44" s="1">
         <v>30001</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J44" s="1">
         <v>5</v>
@@ -2984,25 +2981,25 @@
         <v>300002</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="1">
         <v>30001</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J45" s="1">
         <v>6</v>
@@ -3014,25 +3011,25 @@
         <v>300003</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H46" s="1">
         <v>30001</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J46" s="1">
         <v>7</v>
@@ -3044,25 +3041,25 @@
         <v>300004</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H47" s="1">
         <v>30001</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J47" s="1">
         <v>8</v>
@@ -3074,25 +3071,25 @@
         <v>300005</v>
       </c>
       <c r="C48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H48" s="1">
         <v>30001</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J48" s="1">
         <v>10</v>
@@ -3104,25 +3101,25 @@
         <v>300006</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H49" s="1">
         <v>30002</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J49" s="1">
         <v>10</v>
@@ -3133,25 +3130,25 @@
         <v>300007</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="1">
         <v>30002</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J50" s="1">
         <v>20</v>
@@ -3162,25 +3159,25 @@
         <v>300008</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H51" s="1">
         <v>30002</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J51" s="1">
         <v>30</v>
@@ -3191,25 +3188,25 @@
         <v>300009</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H52" s="1">
         <v>30002</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J52" s="1">
         <v>40</v>
@@ -3220,25 +3217,25 @@
         <v>300010</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H53" s="1">
         <v>30002</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J53" s="1">
         <v>50</v>
@@ -3249,25 +3246,25 @@
         <v>300011</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H54" s="1">
         <v>30003</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J54" s="1">
         <v>2.5</v>
@@ -3278,25 +3275,25 @@
         <v>300012</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="1">
         <v>30003</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J55" s="1">
         <v>5</v>
@@ -3307,25 +3304,25 @@
         <v>300013</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H56" s="1">
         <v>30003</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J56" s="1">
         <v>10</v>
@@ -3336,25 +3333,25 @@
         <v>300014</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H57" s="1">
         <v>30003</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J57" s="1">
         <v>12</v>
@@ -3365,25 +3362,25 @@
         <v>300015</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G58" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H58" s="1">
         <v>30003</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J58" s="1">
         <v>15</v>
@@ -3449,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -3458,40 +3455,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="14" t="s">
+      <c r="H2" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -3500,40 +3497,40 @@
         <v>4</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3545,7 +3542,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -3579,7 +3576,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1">
         <v>5</v>
@@ -3613,7 +3610,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3628,7 +3625,7 @@
         <v>-0.02</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -3647,7 +3644,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3681,7 +3678,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3715,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3730,7 +3727,7 @@
         <v>-0.02</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="7">
         <v>0.01</v>
@@ -3748,7 +3745,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3763,7 +3760,7 @@
         <v>-0.02</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="1">
         <v>0.5</v>
@@ -3777,7 +3774,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3792,7 +3789,7 @@
         <v>-0.02</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1">
         <v>0.02</v>
@@ -3806,7 +3803,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3820,11 +3817,11 @@
       <c r="H12" s="1">
         <v>-0.02</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>14</v>
+      <c r="I12" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="J12" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -3835,7 +3832,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -3850,7 +3847,7 @@
         <v>-0.02</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -3864,7 +3861,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -3879,7 +3876,7 @@
         <v>-0.02</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" s="1">
         <v>1.5</v>
@@ -3930,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
@@ -3944,37 +3941,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="H2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -3983,37 +3980,37 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -124,9 +124,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>OPT_MOVE_SPEED_BONUS_ADD</t>
-  </si>
-  <si>
     <t>OPT_CRIT_RATE_ADD</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -731,6 +728,10 @@
   </si>
   <si>
     <t>EquipSlotTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_MOVE_SPEED_ADD</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1319,52 +1320,52 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1372,28 +1373,28 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1463,16 +1464,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>102</v>
-      </c>
       <c r="E2" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G2" s="8"/>
       <c r="I2" s="8"/>
@@ -1487,16 +1488,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>164</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3" s="8"/>
       <c r="I3" s="8"/>
@@ -1511,13 +1512,13 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" s="1">
         <v>1010101001</v>
@@ -1534,13 +1535,13 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="1">
         <v>1010101002</v>
@@ -1557,13 +1558,13 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="1">
         <v>1010101003</v>
@@ -1580,13 +1581,13 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="1">
         <v>1010101004</v>
@@ -1603,11 +1604,11 @@
         <v>1010202001</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="1">
         <v>1010202001</v>
@@ -1624,11 +1625,11 @@
         <v>1010202002</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9" s="1">
         <v>1010202002</v>
@@ -1645,11 +1646,11 @@
         <v>1010203001</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" s="1">
         <v>1010203001</v>
@@ -1666,11 +1667,11 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" s="1">
         <v>1010203002</v>
@@ -1687,11 +1688,11 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12"/>
       <c r="E12" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="1">
         <v>1010204001</v>
@@ -1708,11 +1709,11 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13"/>
       <c r="E13" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" s="1">
         <v>1010204002</v>
@@ -1729,11 +1730,11 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" s="1">
         <v>1010205001</v>
@@ -1750,11 +1751,11 @@
         <v>1010205002</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="1">
         <v>1010205002</v>
@@ -1771,10 +1772,10 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1">
         <v>1010306001</v>
@@ -1791,10 +1792,10 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="1">
         <v>1010306002</v>
@@ -1811,10 +1812,10 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="1">
         <v>1010307001</v>
@@ -1831,10 +1832,10 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="1">
         <v>1010307002</v>
@@ -1851,10 +1852,10 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="1">
         <v>1010408001</v>
@@ -1871,10 +1872,10 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" s="1">
         <v>1010408002</v>
@@ -2145,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -2168,55 +2169,55 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="R2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -2225,55 +2226,55 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="J3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="P3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="S3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -2285,7 +2286,7 @@
         <v>1010101001</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -2300,10 +2301,10 @@
         <v>17</v>
       </c>
       <c r="I4" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="J4" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -2321,7 +2322,7 @@
         <v>1010101001</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -2336,10 +2337,10 @@
         <v>17</v>
       </c>
       <c r="I5" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="J5" s="11">
-        <v>0.1</v>
+        <v>1.2E-2</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -2363,7 +2364,7 @@
         <v>1010101001</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -2378,16 +2379,16 @@
         <v>17</v>
       </c>
       <c r="I6" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="11">
-        <v>0.1</v>
+        <v>1.4E-2</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" s="1">
         <v>0.1</v>
@@ -2405,7 +2406,7 @@
         <v>1010101001</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
@@ -2420,16 +2421,16 @@
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>70</v>
+        <v>0.25</v>
       </c>
       <c r="J7" s="11">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R7" s="1">
         <v>0.5</v>
@@ -2447,7 +2448,7 @@
         <v>1010101001</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -2462,16 +2463,16 @@
         <v>17</v>
       </c>
       <c r="I8" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="11">
-        <v>0.1</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R8" s="1">
         <v>0.2</v>
@@ -2489,7 +2490,7 @@
         <v>1010101001</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -2504,16 +2505,16 @@
         <v>17</v>
       </c>
       <c r="I9" s="11">
-        <v>110</v>
+        <v>0.4</v>
       </c>
       <c r="J9" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9" s="11">
         <v>0.2</v>
@@ -2531,7 +2532,7 @@
         <v>1010101002</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -2546,10 +2547,10 @@
         <v>17</v>
       </c>
       <c r="I10" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="J10" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="K10" s="8"/>
       <c r="M10" s="8"/>
@@ -2568,7 +2569,7 @@
         <v>1010101002</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
@@ -2583,10 +2584,10 @@
         <v>17</v>
       </c>
       <c r="I11" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="J11" s="11">
-        <v>0.1</v>
+        <v>1.2E-2</v>
       </c>
       <c r="K11" s="8"/>
       <c r="M11" s="8"/>
@@ -2611,7 +2612,7 @@
         <v>1010101002</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>16</v>
@@ -2626,17 +2627,17 @@
         <v>17</v>
       </c>
       <c r="I12" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="J12" s="11">
-        <v>0.1</v>
+        <v>1.4E-2</v>
       </c>
       <c r="K12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R12" s="1">
         <v>0.1</v>
@@ -2654,7 +2655,7 @@
         <v>1010101002</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>16</v>
@@ -2669,17 +2670,17 @@
         <v>17</v>
       </c>
       <c r="I13" s="1">
-        <v>70</v>
+        <v>0.25</v>
       </c>
       <c r="J13" s="11">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="K13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" s="1">
         <v>0.5</v>
@@ -2697,7 +2698,7 @@
         <v>1010101002</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
@@ -2712,17 +2713,17 @@
         <v>17</v>
       </c>
       <c r="I14" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="J14" s="11">
-        <v>0.1</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="K14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R14" s="1">
         <v>0.2</v>
@@ -2740,7 +2741,7 @@
         <v>1010101002</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -2755,16 +2756,16 @@
         <v>17</v>
       </c>
       <c r="I15" s="11">
-        <v>110</v>
+        <v>0.4</v>
       </c>
       <c r="J15" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R15" s="11">
         <v>0.2</v>
@@ -2782,7 +2783,7 @@
         <v>1010101003</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
@@ -2797,10 +2798,10 @@
         <v>17</v>
       </c>
       <c r="I16" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="J16" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -2818,7 +2819,7 @@
         <v>1010101003</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>16</v>
@@ -2833,10 +2834,10 @@
         <v>17</v>
       </c>
       <c r="I17" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="J17" s="11">
-        <v>0.1</v>
+        <v>1.2E-2</v>
       </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -2860,7 +2861,7 @@
         <v>1010101003</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>16</v>
@@ -2875,16 +2876,16 @@
         <v>17</v>
       </c>
       <c r="I18" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="J18" s="11">
-        <v>0.1</v>
+        <v>1.4E-2</v>
       </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R18" s="1">
         <v>0.1</v>
@@ -2902,7 +2903,7 @@
         <v>1010101003</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
@@ -2917,16 +2918,16 @@
         <v>17</v>
       </c>
       <c r="I19" s="1">
-        <v>70</v>
+        <v>0.25</v>
       </c>
       <c r="J19" s="11">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="1">
         <v>0.5</v>
@@ -2944,7 +2945,7 @@
         <v>1010101003</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>16</v>
@@ -2959,17 +2960,17 @@
         <v>17</v>
       </c>
       <c r="I20" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="J20" s="11">
-        <v>0.1</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="K20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R20" s="1">
         <v>0.2</v>
@@ -2987,7 +2988,7 @@
         <v>1010101003</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>16</v>
@@ -3002,17 +3003,17 @@
         <v>17</v>
       </c>
       <c r="I21" s="11">
-        <v>110</v>
+        <v>0.4</v>
       </c>
       <c r="J21" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="K21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R21" s="11">
         <v>0.2</v>
@@ -3030,7 +3031,7 @@
         <v>1010101004</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>16</v>
@@ -3045,10 +3046,10 @@
         <v>18</v>
       </c>
       <c r="I22" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="J22" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="K22" s="8"/>
       <c r="M22" s="8"/>
@@ -3067,7 +3068,7 @@
         <v>1010101004</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
@@ -3082,10 +3083,10 @@
         <v>18</v>
       </c>
       <c r="I23" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="J23" s="11">
-        <v>0.1</v>
+        <v>1.2E-2</v>
       </c>
       <c r="K23" s="8"/>
       <c r="M23" s="8"/>
@@ -3110,7 +3111,7 @@
         <v>1010101004</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
@@ -3125,17 +3126,17 @@
         <v>18</v>
       </c>
       <c r="I24" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="J24" s="11">
-        <v>0.1</v>
+        <v>1.4E-2</v>
       </c>
       <c r="K24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R24" s="1">
         <v>0.1</v>
@@ -3153,7 +3154,7 @@
         <v>1010101004</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
@@ -3168,17 +3169,17 @@
         <v>18</v>
       </c>
       <c r="I25" s="1">
-        <v>70</v>
+        <v>0.25</v>
       </c>
       <c r="J25" s="11">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="K25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R25" s="1">
         <v>0.5</v>
@@ -3196,7 +3197,7 @@
         <v>1010101004</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>16</v>
@@ -3211,17 +3212,17 @@
         <v>18</v>
       </c>
       <c r="I26" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="J26" s="11">
-        <v>0.1</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="K26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R26" s="1">
         <v>0.2</v>
@@ -3239,7 +3240,7 @@
         <v>1010101004</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
@@ -3254,17 +3255,17 @@
         <v>18</v>
       </c>
       <c r="I27" s="11">
-        <v>110</v>
+        <v>0.4</v>
       </c>
       <c r="J27" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="K27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R27" s="11">
         <v>0.2</v>
@@ -3282,7 +3283,7 @@
         <v>1010202001</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>19</v>
@@ -3310,7 +3311,7 @@
         <v>1010202001</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>19</v>
@@ -3326,7 +3327,7 @@
       <c r="N29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R29" s="1">
         <v>100</v>
@@ -3344,7 +3345,7 @@
         <v>1010202001</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>19</v>
@@ -3360,7 +3361,7 @@
       <c r="N30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R30" s="1">
         <v>100</v>
@@ -3378,7 +3379,7 @@
         <v>1010202001</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>19</v>
@@ -3394,7 +3395,7 @@
       <c r="N31" s="8"/>
       <c r="P31" s="8"/>
       <c r="Q31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R31" s="1">
         <v>150</v>
@@ -3412,7 +3413,7 @@
         <v>1010202001</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>19</v>
@@ -3428,7 +3429,7 @@
       <c r="N32" s="8"/>
       <c r="P32" s="8"/>
       <c r="Q32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R32" s="1">
         <v>150</v>
@@ -3446,7 +3447,7 @@
         <v>1010202001</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>19</v>
@@ -3462,7 +3463,7 @@
       <c r="N33" s="8"/>
       <c r="P33" s="8"/>
       <c r="Q33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R33" s="11">
         <v>200</v>
@@ -3480,7 +3481,7 @@
         <v>1010202002</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>19</v>
@@ -3508,7 +3509,7 @@
         <v>1010202002</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>19</v>
@@ -3524,7 +3525,7 @@
       <c r="N35" s="8"/>
       <c r="P35" s="8"/>
       <c r="Q35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R35" s="1">
         <v>100</v>
@@ -3542,7 +3543,7 @@
         <v>1010202002</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>19</v>
@@ -3558,7 +3559,7 @@
       <c r="N36" s="8"/>
       <c r="P36" s="8"/>
       <c r="Q36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R36" s="1">
         <v>100</v>
@@ -3576,7 +3577,7 @@
         <v>1010202002</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>19</v>
@@ -3592,7 +3593,7 @@
       <c r="N37" s="8"/>
       <c r="P37" s="8"/>
       <c r="Q37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R37" s="1">
         <v>150</v>
@@ -3610,7 +3611,7 @@
         <v>1010202002</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>19</v>
@@ -3624,7 +3625,7 @@
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
       <c r="Q38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R38" s="1">
         <v>150</v>
@@ -3642,7 +3643,7 @@
         <v>1010202002</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>19</v>
@@ -3654,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R39" s="11">
         <v>200</v>
@@ -3671,7 +3672,7 @@
         <v>1010203001</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>20</v>
@@ -3691,7 +3692,7 @@
         <v>1010203001</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>20</v>
@@ -3720,7 +3721,7 @@
         <v>1010203001</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>20</v>
@@ -3750,7 +3751,7 @@
         <v>1010203001</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>20</v>
@@ -3782,7 +3783,7 @@
         <v>1010203001</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>20</v>
@@ -3813,7 +3814,7 @@
         <v>1010203001</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>20</v>
@@ -3844,7 +3845,7 @@
         <v>1010203002</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>20</v>
@@ -3866,7 +3867,7 @@
         <v>1010203002</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>20</v>
@@ -3898,7 +3899,7 @@
         <v>1010203002</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>20</v>
@@ -3930,7 +3931,7 @@
         <v>1010203002</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>20</v>
@@ -3959,7 +3960,7 @@
         <v>1010203002</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>20</v>
@@ -3988,7 +3989,7 @@
         <v>1010203002</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>20</v>
@@ -4017,7 +4018,7 @@
         <v>1010204001</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>21</v>
@@ -4038,7 +4039,7 @@
         <v>1010204001</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>21</v>
@@ -4067,7 +4068,7 @@
         <v>1010204001</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>21</v>
@@ -4096,7 +4097,7 @@
         <v>1010204001</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>21</v>
@@ -4125,7 +4126,7 @@
         <v>1010204001</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>21</v>
@@ -4154,7 +4155,7 @@
         <v>1010204001</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>21</v>
@@ -4184,7 +4185,7 @@
         <v>1010204002</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>21</v>
@@ -4204,7 +4205,7 @@
         <v>1010204002</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>21</v>
@@ -4233,7 +4234,7 @@
         <v>1010204002</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>21</v>
@@ -4262,7 +4263,7 @@
         <v>1010204002</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>21</v>
@@ -4291,7 +4292,7 @@
         <v>1010204002</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>21</v>
@@ -4321,7 +4322,7 @@
         <v>1010204002</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>21</v>
@@ -4350,10 +4351,10 @@
         <v>1010205001</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F64" s="1">
         <v>0.1</v>
@@ -4370,10 +4371,10 @@
         <v>1010205001</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F65" s="1">
         <v>0.125</v>
@@ -4382,7 +4383,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R65" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4399,10 +4400,10 @@
         <v>1010205001</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F66" s="1">
         <v>0.15</v>
@@ -4411,7 +4412,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R66" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4428,10 +4429,10 @@
         <v>1010205001</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F67" s="1">
         <v>0.17499999999999999</v>
@@ -4440,7 +4441,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R67" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4458,10 +4459,10 @@
         <v>1010205001</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F68" s="1">
         <v>0.2</v>
@@ -4470,7 +4471,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R68" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4487,10 +4488,10 @@
         <v>1010205001</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F69" s="1">
         <v>0.22500000000000001</v>
@@ -4499,7 +4500,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R69" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4516,10 +4517,10 @@
         <v>1010205002</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F70" s="1">
         <v>0.1</v>
@@ -4536,10 +4537,10 @@
         <v>1010205002</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F71" s="1">
         <v>0.125</v>
@@ -4548,7 +4549,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R71" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4565,10 +4566,10 @@
         <v>1010205002</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F72" s="1">
         <v>0.15</v>
@@ -4577,7 +4578,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R72" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4595,10 +4596,10 @@
         <v>1010205002</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F73" s="1">
         <v>0.17499999999999999</v>
@@ -4607,7 +4608,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R73" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4624,10 +4625,10 @@
         <v>1010205002</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F74" s="1">
         <v>0.2</v>
@@ -4636,7 +4637,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R74" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4653,10 +4654,10 @@
         <v>1010205002</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F75" s="1">
         <v>0.22500000000000001</v>
@@ -4665,7 +4666,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="R75" s="1">
         <v>2.5000000000000001E-2</v>
@@ -4682,7 +4683,7 @@
         <v>1010306001</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -4705,7 +4706,7 @@
         <v>1010306001</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E77" t="s">
         <v>17</v>
@@ -4734,7 +4735,7 @@
         <v>1010306001</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E78" t="s">
         <v>17</v>
@@ -4763,7 +4764,7 @@
         <v>1010306001</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
@@ -4792,7 +4793,7 @@
         <v>1010306001</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -4821,7 +4822,7 @@
         <v>1010306001</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E81" t="s">
         <v>17</v>
@@ -4850,10 +4851,10 @@
         <v>1010306002</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F82" s="11">
         <v>10</v>
@@ -4873,7 +4874,7 @@
         <v>1010306002</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E83" t="s">
         <v>18</v>
@@ -4885,7 +4886,7 @@
         <v>0.1</v>
       </c>
       <c r="Q83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R83" s="1">
         <v>15</v>
@@ -4902,7 +4903,7 @@
         <v>1010306002</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E84" t="s">
         <v>18</v>
@@ -4914,7 +4915,7 @@
         <v>0.1</v>
       </c>
       <c r="Q84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R84" s="1">
         <v>15</v>
@@ -4931,7 +4932,7 @@
         <v>1010306002</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E85" t="s">
         <v>18</v>
@@ -4943,7 +4944,7 @@
         <v>0.1</v>
       </c>
       <c r="Q85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R85" s="1">
         <v>20</v>
@@ -4960,7 +4961,7 @@
         <v>1010306002</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E86" t="s">
         <v>18</v>
@@ -4972,7 +4973,7 @@
         <v>0.1</v>
       </c>
       <c r="Q86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R86" s="1">
         <v>20</v>
@@ -4989,7 +4990,7 @@
         <v>1010306002</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
@@ -5001,7 +5002,7 @@
         <v>0.1</v>
       </c>
       <c r="Q87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R87" s="1">
         <v>25</v>
@@ -5018,7 +5019,7 @@
         <v>1010307001</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
@@ -5041,7 +5042,7 @@
         <v>1010307001</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -5070,7 +5071,7 @@
         <v>1010307001</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E90" t="s">
         <v>17</v>
@@ -5099,7 +5100,7 @@
         <v>1010307001</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E91" t="s">
         <v>17</v>
@@ -5128,7 +5129,7 @@
         <v>1010307001</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -5157,7 +5158,7 @@
         <v>1010307001</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
@@ -5186,10 +5187,10 @@
         <v>1010307002</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F94" s="11">
         <v>10</v>
@@ -5209,7 +5210,7 @@
         <v>1010307002</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E95" t="s">
         <v>18</v>
@@ -5221,7 +5222,7 @@
         <v>0.1</v>
       </c>
       <c r="Q95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R95" s="1">
         <v>15</v>
@@ -5238,7 +5239,7 @@
         <v>1010307002</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E96" t="s">
         <v>18</v>
@@ -5250,7 +5251,7 @@
         <v>0.1</v>
       </c>
       <c r="Q96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R96" s="1">
         <v>15</v>
@@ -5267,7 +5268,7 @@
         <v>1010307002</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E97" t="s">
         <v>18</v>
@@ -5279,7 +5280,7 @@
         <v>0.1</v>
       </c>
       <c r="Q97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R97" s="1">
         <v>20</v>
@@ -5296,7 +5297,7 @@
         <v>1010307002</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E98" t="s">
         <v>18</v>
@@ -5308,7 +5309,7 @@
         <v>0.1</v>
       </c>
       <c r="Q98" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R98" s="1">
         <v>20</v>
@@ -5325,7 +5326,7 @@
         <v>1010307002</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E99" t="s">
         <v>18</v>
@@ -5337,7 +5338,7 @@
         <v>0.1</v>
       </c>
       <c r="Q99" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R99" s="1">
         <v>25</v>
@@ -5354,7 +5355,7 @@
         <v>1010408001</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -5377,7 +5378,7 @@
         <v>1010408001</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -5406,7 +5407,7 @@
         <v>1010408001</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E102" t="s">
         <v>17</v>
@@ -5435,7 +5436,7 @@
         <v>1010408001</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E103" t="s">
         <v>17</v>
@@ -5464,7 +5465,7 @@
         <v>1010408001</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E104" t="s">
         <v>17</v>
@@ -5493,7 +5494,7 @@
         <v>1010408001</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E105" t="s">
         <v>17</v>
@@ -5522,10 +5523,10 @@
         <v>1010408002</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E106" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F106" s="11">
         <v>10</v>
@@ -5545,7 +5546,7 @@
         <v>1010408002</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E107" t="s">
         <v>18</v>
@@ -5557,7 +5558,7 @@
         <v>0.1</v>
       </c>
       <c r="Q107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R107" s="1">
         <v>15</v>
@@ -5574,7 +5575,7 @@
         <v>1010408002</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
@@ -5586,7 +5587,7 @@
         <v>0.1</v>
       </c>
       <c r="Q108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R108" s="1">
         <v>15</v>
@@ -5603,7 +5604,7 @@
         <v>1010408002</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E109" t="s">
         <v>18</v>
@@ -5615,7 +5616,7 @@
         <v>0.1</v>
       </c>
       <c r="Q109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R109" s="1">
         <v>20</v>
@@ -5632,7 +5633,7 @@
         <v>1010408002</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E110" t="s">
         <v>18</v>
@@ -5644,7 +5645,7 @@
         <v>0.1</v>
       </c>
       <c r="Q110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R110" s="1">
         <v>20</v>
@@ -5661,7 +5662,7 @@
         <v>1010408002</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E111" t="s">
         <v>18</v>
@@ -5673,7 +5674,7 @@
         <v>0.1</v>
       </c>
       <c r="Q111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R111" s="1">
         <v>25</v>
@@ -5778,37 +5779,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="L2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -5817,10 +5818,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -5829,7 +5830,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>2</v>
@@ -5838,16 +5839,16 @@
         <v>2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -5859,7 +5860,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -5871,7 +5872,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -5883,7 +5884,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -5894,7 +5895,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -5905,7 +5906,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -5916,7 +5917,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -5925,10 +5926,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -5937,10 +5938,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -5948,10 +5949,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -5959,10 +5960,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -5970,10 +5971,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -5982,10 +5983,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -5994,10 +5995,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -6005,10 +6006,10 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -6016,10 +6017,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -6027,10 +6028,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -6039,10 +6040,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -6050,10 +6051,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -6061,10 +6062,10 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -6072,10 +6073,10 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -6083,10 +6084,10 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -6095,10 +6096,10 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -6106,10 +6107,10 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -6117,10 +6118,10 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -6128,10 +6129,10 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -6139,10 +6140,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -6151,10 +6152,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -6162,10 +6163,10 @@
         <v>28</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -6173,10 +6174,10 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -6184,10 +6185,10 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -6195,10 +6196,10 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -6207,10 +6208,10 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -6218,10 +6219,10 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -6229,10 +6230,10 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -6240,10 +6241,10 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -6251,10 +6252,10 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -6263,10 +6264,10 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -6274,10 +6275,10 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -6285,10 +6286,10 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -6296,10 +6297,10 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -6307,10 +6308,10 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -6318,10 +6319,10 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -6329,10 +6330,10 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -6340,10 +6341,10 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -6351,10 +6352,10 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
@@ -6362,10 +6363,10 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
@@ -6373,10 +6374,10 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
@@ -6384,10 +6385,10 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
@@ -6429,10 +6430,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -6444,25 +6445,25 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -6471,7 +6472,7 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>5</v>
@@ -6486,7 +6487,7 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>6</v>
@@ -6501,7 +6502,7 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>7</v>
@@ -6515,7 +6516,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>8</v>
@@ -6529,7 +6530,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>9</v>
@@ -6543,7 +6544,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>10</v>
@@ -6627,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="10"/>
@@ -6641,43 +6642,43 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="L2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="N2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -6686,13 +6687,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>13</v>
@@ -6719,10 +6720,10 @@
         <v>13</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -6817,7 +6818,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>5</v>
@@ -6831,7 +6832,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -6845,7 +6846,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>7</v>
@@ -6859,7 +6860,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>8</v>
@@ -6874,7 +6875,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>9</v>
@@ -6888,7 +6889,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>10</v>
@@ -6900,7 +6901,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>5</v>
@@ -6914,7 +6915,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -6929,7 +6930,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>7</v>
@@ -6943,7 +6944,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>8</v>
@@ -6957,7 +6958,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>9</v>
@@ -6971,7 +6972,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>10</v>
@@ -6984,7 +6985,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>5</v>
@@ -6998,7 +6999,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -7012,7 +7013,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>7</v>
@@ -7026,7 +7027,7 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>8</v>
@@ -7041,7 +7042,7 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>9</v>
@@ -7055,7 +7056,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>10</v>
@@ -7067,7 +7068,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>5</v>
@@ -7081,7 +7082,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>6</v>
@@ -7096,7 +7097,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>7</v>
@@ -7110,7 +7111,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>8</v>
@@ -7124,7 +7125,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>9</v>
@@ -7138,7 +7139,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>10</v>
@@ -7151,7 +7152,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>5</v>
@@ -7165,7 +7166,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>6</v>
@@ -7179,7 +7180,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>7</v>
@@ -7193,7 +7194,7 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>8</v>
@@ -7207,7 +7208,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>9</v>
@@ -7221,7 +7222,7 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>10</v>
@@ -7233,7 +7234,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>5</v>
@@ -7247,7 +7248,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>6</v>
@@ -7261,7 +7262,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>7</v>
@@ -7275,7 +7276,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>8</v>
@@ -7289,7 +7290,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>9</v>
@@ -7303,7 +7304,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>10</v>
@@ -7315,7 +7316,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>5</v>
@@ -7329,7 +7330,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
@@ -7343,7 +7344,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>7</v>
@@ -7357,7 +7358,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>8</v>
@@ -7371,7 +7372,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>9</v>
@@ -7385,7 +7386,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>10</v>
@@ -7414,10 +7415,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="12"/>
@@ -7428,34 +7429,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>144</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -7658,10 +7659,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="12"/>
@@ -7672,49 +7673,49 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1">
         <v>0.6</v>
@@ -7727,16 +7728,16 @@
         <v>0.3</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D5" s="1">
         <v>0.8</v>
@@ -7749,16 +7750,16 @@
         <v>0.35</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -7771,15 +7772,15 @@
         <v>0.22</v>
       </c>
       <c r="G6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D7" s="1">
         <v>1.2</v>
@@ -7792,15 +7793,15 @@
         <v>0.1</v>
       </c>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8" s="1">
         <v>1.4</v>
@@ -7813,7 +7814,7 @@
         <v>0.03</v>
       </c>
       <c r="G8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -7925,10 +7926,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -7941,53 +7942,53 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
         <v>73</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7996,7 +7997,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="1">
         <v>800</v>
@@ -8023,7 +8024,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D5" s="1">
         <v>400</v>
@@ -8050,7 +8051,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -8076,7 +8077,7 @@
         <v>20001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D7" s="1">
         <v>400</v>
@@ -8102,7 +8103,7 @@
         <v>20002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -8129,7 +8130,7 @@
         <v>20003</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8156,7 +8157,7 @@
         <v>30001</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -1294,7 +1294,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2394,7 +2394,7 @@
         <v>0.1</v>
       </c>
       <c r="S6" s="1">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -2436,7 +2436,7 @@
         <v>0.5</v>
       </c>
       <c r="S7" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -2475,10 +2475,10 @@
         <v>24</v>
       </c>
       <c r="R8" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S8" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -2517,10 +2517,10 @@
         <v>26</v>
       </c>
       <c r="R9" s="11">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="S9" s="11">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -2597,7 +2597,7 @@
         <v>21</v>
       </c>
       <c r="R11" s="1">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="S11" s="1">
         <v>0.2</v>
@@ -2643,7 +2643,7 @@
         <v>0.1</v>
       </c>
       <c r="S12" s="1">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2686,7 +2686,7 @@
         <v>0.5</v>
       </c>
       <c r="S13" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -2726,10 +2726,10 @@
         <v>24</v>
       </c>
       <c r="R14" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S14" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -2768,10 +2768,10 @@
         <v>26</v>
       </c>
       <c r="R15" s="11">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="S15" s="11">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -2846,7 +2846,7 @@
         <v>21</v>
       </c>
       <c r="R17" s="1">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="S17" s="1">
         <v>0.2</v>
@@ -2891,7 +2891,7 @@
         <v>0.1</v>
       </c>
       <c r="S18" s="1">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -2933,7 +2933,7 @@
         <v>0.5</v>
       </c>
       <c r="S19" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -2973,10 +2973,10 @@
         <v>24</v>
       </c>
       <c r="R20" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S20" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -3016,10 +3016,10 @@
         <v>26</v>
       </c>
       <c r="R21" s="11">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="S21" s="11">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -3096,7 +3096,7 @@
         <v>21</v>
       </c>
       <c r="R23" s="1">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="S23" s="1">
         <v>0.2</v>
@@ -3142,7 +3142,7 @@
         <v>0.1</v>
       </c>
       <c r="S24" s="1">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -3185,7 +3185,7 @@
         <v>0.5</v>
       </c>
       <c r="S25" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -3225,10 +3225,10 @@
         <v>24</v>
       </c>
       <c r="R26" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S26" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -3268,10 +3268,10 @@
         <v>26</v>
       </c>
       <c r="R27" s="11">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="S27" s="11">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -3333,7 +3333,7 @@
         <v>100</v>
       </c>
       <c r="S29" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -3367,7 +3367,7 @@
         <v>100</v>
       </c>
       <c r="S30" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
@@ -3401,7 +3401,7 @@
         <v>150</v>
       </c>
       <c r="S31" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -3435,7 +3435,7 @@
         <v>150</v>
       </c>
       <c r="S32" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -3469,7 +3469,7 @@
         <v>200</v>
       </c>
       <c r="S33" s="11">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -3531,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="S35" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -3565,7 +3565,7 @@
         <v>100</v>
       </c>
       <c r="S36" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -3599,7 +3599,7 @@
         <v>150</v>
       </c>
       <c r="S37" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
@@ -3631,7 +3631,7 @@
         <v>150</v>
       </c>
       <c r="S38" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
@@ -3661,7 +3661,7 @@
         <v>200</v>
       </c>
       <c r="S39" s="11">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
@@ -3710,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="S41" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -3739,7 +3739,7 @@
         <v>15</v>
       </c>
       <c r="S42" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -3771,7 +3771,7 @@
         <v>20</v>
       </c>
       <c r="S43" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -3803,7 +3803,7 @@
         <v>20</v>
       </c>
       <c r="S44" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
@@ -3834,7 +3834,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
@@ -3887,7 +3887,7 @@
         <v>15</v>
       </c>
       <c r="S47" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -3919,7 +3919,7 @@
         <v>15</v>
       </c>
       <c r="S48" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -3949,7 +3949,7 @@
         <v>20</v>
       </c>
       <c r="S49" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -3978,7 +3978,7 @@
         <v>20</v>
       </c>
       <c r="S50" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
@@ -4007,7 +4007,7 @@
         <v>30</v>
       </c>
       <c r="S51" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
@@ -4057,7 +4057,7 @@
         <v>0.05</v>
       </c>
       <c r="S53" s="1">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
@@ -4083,10 +4083,10 @@
         <v>21</v>
       </c>
       <c r="R54" s="1">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="S54" s="1">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
@@ -4112,10 +4112,10 @@
         <v>21</v>
       </c>
       <c r="R55" s="1">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="S55" s="1">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
@@ -4141,10 +4141,10 @@
         <v>21</v>
       </c>
       <c r="R56" s="1">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="S56" s="1">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
@@ -4170,10 +4170,10 @@
         <v>21</v>
       </c>
       <c r="R57" s="1">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="S57" s="1">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
@@ -4223,7 +4223,7 @@
         <v>0.05</v>
       </c>
       <c r="S59" s="1">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
@@ -4249,10 +4249,10 @@
         <v>21</v>
       </c>
       <c r="R60" s="1">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="S60" s="1">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
@@ -4278,10 +4278,10 @@
         <v>21</v>
       </c>
       <c r="R61" s="1">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="S61" s="1">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
@@ -4307,10 +4307,10 @@
         <v>21</v>
       </c>
       <c r="R62" s="1">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="S62" s="1">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
@@ -4337,10 +4337,10 @@
         <v>21</v>
       </c>
       <c r="R63" s="1">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="S63" s="1">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
@@ -4386,10 +4386,10 @@
         <v>168</v>
       </c>
       <c r="R65" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="S65" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
@@ -4415,10 +4415,10 @@
         <v>168</v>
       </c>
       <c r="R66" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S66" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
@@ -4444,10 +4444,10 @@
         <v>168</v>
       </c>
       <c r="R67" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
       <c r="S67" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
@@ -4474,10 +4474,10 @@
         <v>168</v>
       </c>
       <c r="R68" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.2</v>
       </c>
       <c r="S68" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
@@ -4503,10 +4503,10 @@
         <v>168</v>
       </c>
       <c r="R69" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.25</v>
       </c>
       <c r="S69" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
@@ -4552,10 +4552,10 @@
         <v>168</v>
       </c>
       <c r="R71" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="S71" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
@@ -4581,10 +4581,10 @@
         <v>168</v>
       </c>
       <c r="R72" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S72" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
@@ -4611,10 +4611,10 @@
         <v>168</v>
       </c>
       <c r="R73" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
       <c r="S73" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
@@ -4640,10 +4640,10 @@
         <v>168</v>
       </c>
       <c r="R74" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.2</v>
       </c>
       <c r="S74" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.3">
@@ -4669,10 +4669,10 @@
         <v>168</v>
       </c>
       <c r="R75" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.25</v>
       </c>
       <c r="S75" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.3">
@@ -4689,10 +4689,10 @@
         <v>17</v>
       </c>
       <c r="F76" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G76" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Q76"/>
       <c r="R76" s="11"/>
@@ -4712,19 +4712,19 @@
         <v>17</v>
       </c>
       <c r="F77" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G77" s="11">
-        <v>0.1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q77" t="s">
         <v>17</v>
       </c>
-      <c r="R77" s="1">
-        <v>15</v>
-      </c>
-      <c r="S77" s="1">
-        <v>15</v>
+      <c r="R77" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="S77" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
@@ -4741,19 +4741,19 @@
         <v>17</v>
       </c>
       <c r="F78" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="G78" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q78" t="s">
         <v>17</v>
       </c>
       <c r="R78" s="1">
-        <v>15</v>
-      </c>
-      <c r="S78" s="1">
-        <v>15</v>
+        <v>0.15</v>
+      </c>
+      <c r="S78" s="11">
+        <v>0.3</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
@@ -4769,20 +4769,20 @@
       <c r="E79" t="s">
         <v>17</v>
       </c>
-      <c r="F79" s="1">
-        <v>70</v>
+      <c r="F79" s="11">
+        <v>0.25</v>
       </c>
       <c r="G79" s="11">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q79" t="s">
         <v>17</v>
       </c>
       <c r="R79" s="1">
-        <v>20</v>
-      </c>
-      <c r="S79" s="1">
-        <v>20</v>
+        <v>0.2</v>
+      </c>
+      <c r="S79" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
@@ -4799,19 +4799,19 @@
         <v>17</v>
       </c>
       <c r="F80" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="G80" s="11">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q80" t="s">
         <v>17</v>
       </c>
-      <c r="R80" s="1">
-        <v>20</v>
-      </c>
-      <c r="S80" s="1">
-        <v>20</v>
+      <c r="R80" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="S80" s="11">
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.3">
@@ -4828,19 +4828,19 @@
         <v>17</v>
       </c>
       <c r="F81" s="11">
-        <v>110</v>
+        <v>0.35</v>
       </c>
       <c r="G81" s="11">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q81" t="s">
         <v>17</v>
       </c>
       <c r="R81" s="1">
-        <v>25</v>
-      </c>
-      <c r="S81" s="1">
-        <v>25</v>
+        <v>0.3</v>
+      </c>
+      <c r="S81" s="11">
+        <v>0.6</v>
       </c>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.3">
@@ -4857,10 +4857,10 @@
         <v>38</v>
       </c>
       <c r="F82" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G82" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Q82"/>
       <c r="R82" s="11"/>
@@ -4880,19 +4880,19 @@
         <v>18</v>
       </c>
       <c r="F83" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G83" s="11">
-        <v>0.1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q83" t="s">
         <v>38</v>
       </c>
-      <c r="R83" s="1">
-        <v>15</v>
-      </c>
-      <c r="S83" s="1">
-        <v>15</v>
+      <c r="R83" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="S83" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="84" spans="2:19" x14ac:dyDescent="0.3">
@@ -4909,19 +4909,19 @@
         <v>18</v>
       </c>
       <c r="F84" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="G84" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q84" t="s">
         <v>38</v>
       </c>
       <c r="R84" s="1">
-        <v>15</v>
-      </c>
-      <c r="S84" s="1">
-        <v>15</v>
+        <v>0.15</v>
+      </c>
+      <c r="S84" s="11">
+        <v>0.3</v>
       </c>
     </row>
     <row r="85" spans="2:19" x14ac:dyDescent="0.3">
@@ -4937,20 +4937,20 @@
       <c r="E85" t="s">
         <v>18</v>
       </c>
-      <c r="F85" s="1">
-        <v>70</v>
+      <c r="F85" s="11">
+        <v>0.25</v>
       </c>
       <c r="G85" s="11">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q85" t="s">
         <v>38</v>
       </c>
       <c r="R85" s="1">
-        <v>20</v>
-      </c>
-      <c r="S85" s="1">
-        <v>20</v>
+        <v>0.2</v>
+      </c>
+      <c r="S85" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="86" spans="2:19" x14ac:dyDescent="0.3">
@@ -4967,19 +4967,19 @@
         <v>18</v>
       </c>
       <c r="F86" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="G86" s="11">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q86" t="s">
         <v>38</v>
       </c>
-      <c r="R86" s="1">
-        <v>20</v>
-      </c>
-      <c r="S86" s="1">
-        <v>20</v>
+      <c r="R86" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="S86" s="11">
+        <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
@@ -4996,19 +4996,19 @@
         <v>18</v>
       </c>
       <c r="F87" s="11">
-        <v>110</v>
+        <v>0.35</v>
       </c>
       <c r="G87" s="11">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q87" t="s">
         <v>38</v>
       </c>
       <c r="R87" s="1">
-        <v>25</v>
-      </c>
-      <c r="S87" s="1">
-        <v>25</v>
+        <v>0.3</v>
+      </c>
+      <c r="S87" s="11">
+        <v>0.6</v>
       </c>
     </row>
     <row r="88" spans="2:19" x14ac:dyDescent="0.3">
@@ -5025,10 +5025,10 @@
         <v>17</v>
       </c>
       <c r="F88" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G88" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Q88"/>
       <c r="R88" s="11"/>
@@ -5048,19 +5048,19 @@
         <v>17</v>
       </c>
       <c r="F89" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G89" s="11">
-        <v>0.1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q89" t="s">
         <v>17</v>
       </c>
-      <c r="R89" s="1">
-        <v>15</v>
-      </c>
-      <c r="S89" s="1">
-        <v>15</v>
+      <c r="R89" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="S89" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="90" spans="2:19" x14ac:dyDescent="0.3">
@@ -5077,19 +5077,19 @@
         <v>17</v>
       </c>
       <c r="F90" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="G90" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q90" t="s">
         <v>17</v>
       </c>
       <c r="R90" s="1">
-        <v>15</v>
-      </c>
-      <c r="S90" s="1">
-        <v>15</v>
+        <v>0.15</v>
+      </c>
+      <c r="S90" s="11">
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:19" x14ac:dyDescent="0.3">
@@ -5105,20 +5105,20 @@
       <c r="E91" t="s">
         <v>17</v>
       </c>
-      <c r="F91" s="1">
-        <v>70</v>
+      <c r="F91" s="11">
+        <v>0.25</v>
       </c>
       <c r="G91" s="11">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q91" t="s">
         <v>17</v>
       </c>
       <c r="R91" s="1">
-        <v>20</v>
-      </c>
-      <c r="S91" s="1">
-        <v>20</v>
+        <v>0.2</v>
+      </c>
+      <c r="S91" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.3">
@@ -5135,19 +5135,19 @@
         <v>17</v>
       </c>
       <c r="F92" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="G92" s="11">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q92" t="s">
         <v>17</v>
       </c>
-      <c r="R92" s="1">
-        <v>20</v>
-      </c>
-      <c r="S92" s="1">
-        <v>20</v>
+      <c r="R92" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="S92" s="11">
+        <v>0.5</v>
       </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.3">
@@ -5164,19 +5164,19 @@
         <v>17</v>
       </c>
       <c r="F93" s="11">
-        <v>110</v>
+        <v>0.35</v>
       </c>
       <c r="G93" s="11">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q93" t="s">
         <v>17</v>
       </c>
       <c r="R93" s="1">
-        <v>25</v>
-      </c>
-      <c r="S93" s="1">
-        <v>25</v>
+        <v>0.3</v>
+      </c>
+      <c r="S93" s="11">
+        <v>0.6</v>
       </c>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.3">
@@ -5193,10 +5193,10 @@
         <v>38</v>
       </c>
       <c r="F94" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G94" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Q94"/>
       <c r="R94" s="11"/>
@@ -5216,19 +5216,19 @@
         <v>18</v>
       </c>
       <c r="F95" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G95" s="11">
-        <v>0.1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q95" t="s">
         <v>38</v>
       </c>
-      <c r="R95" s="1">
-        <v>15</v>
-      </c>
-      <c r="S95" s="1">
-        <v>15</v>
+      <c r="R95" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="S95" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.3">
@@ -5245,19 +5245,19 @@
         <v>18</v>
       </c>
       <c r="F96" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="G96" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q96" t="s">
         <v>38</v>
       </c>
       <c r="R96" s="1">
-        <v>15</v>
-      </c>
-      <c r="S96" s="1">
-        <v>15</v>
+        <v>0.15</v>
+      </c>
+      <c r="S96" s="11">
+        <v>0.3</v>
       </c>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
@@ -5273,20 +5273,20 @@
       <c r="E97" t="s">
         <v>18</v>
       </c>
-      <c r="F97" s="1">
-        <v>70</v>
+      <c r="F97" s="11">
+        <v>0.25</v>
       </c>
       <c r="G97" s="11">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q97" t="s">
         <v>38</v>
       </c>
       <c r="R97" s="1">
-        <v>20</v>
-      </c>
-      <c r="S97" s="1">
-        <v>20</v>
+        <v>0.2</v>
+      </c>
+      <c r="S97" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.3">
@@ -5303,19 +5303,19 @@
         <v>18</v>
       </c>
       <c r="F98" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="G98" s="11">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q98" t="s">
         <v>38</v>
       </c>
-      <c r="R98" s="1">
-        <v>20</v>
-      </c>
-      <c r="S98" s="1">
-        <v>20</v>
+      <c r="R98" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="S98" s="11">
+        <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.3">
@@ -5332,19 +5332,19 @@
         <v>18</v>
       </c>
       <c r="F99" s="11">
-        <v>110</v>
+        <v>0.35</v>
       </c>
       <c r="G99" s="11">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q99" t="s">
         <v>38</v>
       </c>
       <c r="R99" s="1">
-        <v>25</v>
-      </c>
-      <c r="S99" s="1">
-        <v>25</v>
+        <v>0.3</v>
+      </c>
+      <c r="S99" s="11">
+        <v>0.6</v>
       </c>
     </row>
     <row r="100" spans="2:19" x14ac:dyDescent="0.3">
@@ -5361,10 +5361,10 @@
         <v>17</v>
       </c>
       <c r="F100" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G100" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Q100"/>
       <c r="R100" s="11"/>
@@ -5384,19 +5384,19 @@
         <v>17</v>
       </c>
       <c r="F101" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G101" s="11">
-        <v>0.1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q101" t="s">
         <v>17</v>
       </c>
-      <c r="R101" s="1">
-        <v>15</v>
-      </c>
-      <c r="S101" s="1">
-        <v>15</v>
+      <c r="R101" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="S101" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="102" spans="2:19" x14ac:dyDescent="0.3">
@@ -5413,19 +5413,19 @@
         <v>17</v>
       </c>
       <c r="F102" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="G102" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q102" t="s">
         <v>17</v>
       </c>
       <c r="R102" s="1">
-        <v>15</v>
-      </c>
-      <c r="S102" s="1">
-        <v>15</v>
+        <v>0.15</v>
+      </c>
+      <c r="S102" s="11">
+        <v>0.3</v>
       </c>
     </row>
     <row r="103" spans="2:19" x14ac:dyDescent="0.3">
@@ -5441,20 +5441,20 @@
       <c r="E103" t="s">
         <v>17</v>
       </c>
-      <c r="F103" s="1">
-        <v>70</v>
+      <c r="F103" s="11">
+        <v>0.25</v>
       </c>
       <c r="G103" s="11">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q103" t="s">
         <v>17</v>
       </c>
       <c r="R103" s="1">
-        <v>20</v>
-      </c>
-      <c r="S103" s="1">
-        <v>20</v>
+        <v>0.2</v>
+      </c>
+      <c r="S103" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="104" spans="2:19" x14ac:dyDescent="0.3">
@@ -5471,19 +5471,19 @@
         <v>17</v>
       </c>
       <c r="F104" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="G104" s="11">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q104" t="s">
         <v>17</v>
       </c>
-      <c r="R104" s="1">
-        <v>20</v>
-      </c>
-      <c r="S104" s="1">
-        <v>20</v>
+      <c r="R104" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="S104" s="11">
+        <v>0.5</v>
       </c>
     </row>
     <row r="105" spans="2:19" x14ac:dyDescent="0.3">
@@ -5500,19 +5500,19 @@
         <v>17</v>
       </c>
       <c r="F105" s="11">
-        <v>110</v>
+        <v>0.35</v>
       </c>
       <c r="G105" s="11">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q105" t="s">
         <v>17</v>
       </c>
       <c r="R105" s="1">
-        <v>25</v>
-      </c>
-      <c r="S105" s="1">
-        <v>25</v>
+        <v>0.3</v>
+      </c>
+      <c r="S105" s="11">
+        <v>0.6</v>
       </c>
     </row>
     <row r="106" spans="2:19" x14ac:dyDescent="0.3">
@@ -5529,10 +5529,10 @@
         <v>38</v>
       </c>
       <c r="F106" s="11">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G106" s="11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="Q106"/>
       <c r="R106" s="11"/>
@@ -5552,19 +5552,19 @@
         <v>18</v>
       </c>
       <c r="F107" s="1">
-        <v>30</v>
+        <v>0.15</v>
       </c>
       <c r="G107" s="11">
-        <v>0.1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q107" t="s">
         <v>38</v>
       </c>
-      <c r="R107" s="1">
-        <v>15</v>
-      </c>
-      <c r="S107" s="1">
-        <v>15</v>
+      <c r="R107" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="S107" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="108" spans="2:19" x14ac:dyDescent="0.3">
@@ -5581,19 +5581,19 @@
         <v>18</v>
       </c>
       <c r="F108" s="1">
-        <v>50</v>
+        <v>0.2</v>
       </c>
       <c r="G108" s="11">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q108" t="s">
         <v>38</v>
       </c>
       <c r="R108" s="1">
-        <v>15</v>
-      </c>
-      <c r="S108" s="1">
-        <v>15</v>
+        <v>0.15</v>
+      </c>
+      <c r="S108" s="11">
+        <v>0.3</v>
       </c>
     </row>
     <row r="109" spans="2:19" x14ac:dyDescent="0.3">
@@ -5609,20 +5609,20 @@
       <c r="E109" t="s">
         <v>18</v>
       </c>
-      <c r="F109" s="1">
-        <v>70</v>
+      <c r="F109" s="11">
+        <v>0.25</v>
       </c>
       <c r="G109" s="11">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q109" t="s">
         <v>38</v>
       </c>
       <c r="R109" s="1">
-        <v>20</v>
-      </c>
-      <c r="S109" s="1">
-        <v>20</v>
+        <v>0.2</v>
+      </c>
+      <c r="S109" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="110" spans="2:19" x14ac:dyDescent="0.3">
@@ -5639,19 +5639,19 @@
         <v>18</v>
       </c>
       <c r="F110" s="1">
-        <v>90</v>
+        <v>0.3</v>
       </c>
       <c r="G110" s="11">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q110" t="s">
         <v>38</v>
       </c>
-      <c r="R110" s="1">
-        <v>20</v>
-      </c>
-      <c r="S110" s="1">
-        <v>20</v>
+      <c r="R110" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="S110" s="11">
+        <v>0.5</v>
       </c>
     </row>
     <row r="111" spans="2:19" x14ac:dyDescent="0.3">
@@ -5668,19 +5668,19 @@
         <v>18</v>
       </c>
       <c r="F111" s="11">
-        <v>110</v>
+        <v>0.35</v>
       </c>
       <c r="G111" s="11">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q111" t="s">
         <v>38</v>
       </c>
       <c r="R111" s="1">
-        <v>25</v>
-      </c>
-      <c r="S111" s="1">
-        <v>25</v>
+        <v>0.3</v>
+      </c>
+      <c r="S111" s="11">
+        <v>0.6</v>
       </c>
     </row>
     <row r="112" spans="2:19" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -201,13 +201,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Greatsword</t>
-  </si>
-  <si>
-    <t>Greatsword</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>RuneSword</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -732,6 +725,14 @@
   </si>
   <si>
     <t>OPT_MOVE_SPEED_ADD</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DualBlades</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DualBlades</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1294,7 +1295,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1320,52 +1321,52 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1373,28 +1374,28 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1464,16 +1465,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G2" s="8"/>
       <c r="I2" s="8"/>
@@ -1488,16 +1489,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G3" s="8"/>
       <c r="I3" s="8"/>
@@ -1512,13 +1513,13 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1">
         <v>1010101001</v>
@@ -1535,13 +1536,13 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F5" s="1">
         <v>1010101002</v>
@@ -1558,13 +1559,13 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F6" s="1">
         <v>1010101003</v>
@@ -1581,13 +1582,13 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="1">
         <v>1010101004</v>
@@ -1604,11 +1605,11 @@
         <v>1010202001</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F8" s="1">
         <v>1010202001</v>
@@ -1625,11 +1626,11 @@
         <v>1010202002</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="1">
         <v>1010202002</v>
@@ -1646,11 +1647,11 @@
         <v>1010203001</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1">
         <v>1010203001</v>
@@ -1667,11 +1668,11 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F11" s="1">
         <v>1010203002</v>
@@ -1688,11 +1689,11 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12"/>
       <c r="E12" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F12" s="1">
         <v>1010204001</v>
@@ -1709,11 +1710,11 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13"/>
       <c r="E13" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" s="1">
         <v>1010204002</v>
@@ -1730,11 +1731,11 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F14" s="1">
         <v>1010205001</v>
@@ -1751,11 +1752,11 @@
         <v>1010205002</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F15" s="1">
         <v>1010205002</v>
@@ -1772,10 +1773,10 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F16" s="1">
         <v>1010306001</v>
@@ -1792,10 +1793,10 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F17" s="1">
         <v>1010306002</v>
@@ -1812,10 +1813,10 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F18" s="1">
         <v>1010307001</v>
@@ -1832,10 +1833,10 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F19" s="1">
         <v>1010307002</v>
@@ -1852,10 +1853,10 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F20" s="1">
         <v>1010408001</v>
@@ -1872,10 +1873,10 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F21" s="1">
         <v>1010408002</v>
@@ -2146,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -2169,55 +2170,55 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="I2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="L2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="O2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -2226,55 +2227,55 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -2286,7 +2287,7 @@
         <v>1010101001</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -2322,7 +2323,7 @@
         <v>1010101001</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -2364,7 +2365,7 @@
         <v>1010101001</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -2406,7 +2407,7 @@
         <v>1010101001</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
@@ -2448,7 +2449,7 @@
         <v>1010101001</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -2490,7 +2491,7 @@
         <v>1010101001</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -2532,7 +2533,7 @@
         <v>1010101002</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -2569,7 +2570,7 @@
         <v>1010101002</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
@@ -2612,7 +2613,7 @@
         <v>1010101002</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>16</v>
@@ -2655,7 +2656,7 @@
         <v>1010101002</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>16</v>
@@ -2698,7 +2699,7 @@
         <v>1010101002</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
@@ -2741,7 +2742,7 @@
         <v>1010101002</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -2783,7 +2784,7 @@
         <v>1010101003</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
@@ -2819,7 +2820,7 @@
         <v>1010101003</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>16</v>
@@ -2861,7 +2862,7 @@
         <v>1010101003</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>16</v>
@@ -2903,7 +2904,7 @@
         <v>1010101003</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
@@ -2945,7 +2946,7 @@
         <v>1010101003</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>16</v>
@@ -2988,7 +2989,7 @@
         <v>1010101003</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>16</v>
@@ -3031,7 +3032,7 @@
         <v>1010101004</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>16</v>
@@ -3068,7 +3069,7 @@
         <v>1010101004</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
@@ -3111,7 +3112,7 @@
         <v>1010101004</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
@@ -3154,7 +3155,7 @@
         <v>1010101004</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
@@ -3197,7 +3198,7 @@
         <v>1010101004</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>16</v>
@@ -3240,7 +3241,7 @@
         <v>1010101004</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
@@ -3283,7 +3284,7 @@
         <v>1010202001</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>19</v>
@@ -3311,7 +3312,7 @@
         <v>1010202001</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>19</v>
@@ -3345,7 +3346,7 @@
         <v>1010202001</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>19</v>
@@ -3379,7 +3380,7 @@
         <v>1010202001</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>19</v>
@@ -3413,7 +3414,7 @@
         <v>1010202001</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>19</v>
@@ -3447,7 +3448,7 @@
         <v>1010202001</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>19</v>
@@ -3481,7 +3482,7 @@
         <v>1010202002</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>19</v>
@@ -3509,7 +3510,7 @@
         <v>1010202002</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>19</v>
@@ -3543,7 +3544,7 @@
         <v>1010202002</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>19</v>
@@ -3577,7 +3578,7 @@
         <v>1010202002</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>19</v>
@@ -3611,7 +3612,7 @@
         <v>1010202002</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>19</v>
@@ -3643,7 +3644,7 @@
         <v>1010202002</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>19</v>
@@ -3672,7 +3673,7 @@
         <v>1010203001</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>20</v>
@@ -3692,7 +3693,7 @@
         <v>1010203001</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>20</v>
@@ -3721,7 +3722,7 @@
         <v>1010203001</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>20</v>
@@ -3751,7 +3752,7 @@
         <v>1010203001</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>20</v>
@@ -3783,7 +3784,7 @@
         <v>1010203001</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>20</v>
@@ -3814,7 +3815,7 @@
         <v>1010203001</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>20</v>
@@ -3845,7 +3846,7 @@
         <v>1010203002</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>20</v>
@@ -3867,7 +3868,7 @@
         <v>1010203002</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>20</v>
@@ -3899,7 +3900,7 @@
         <v>1010203002</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>20</v>
@@ -3931,7 +3932,7 @@
         <v>1010203002</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>20</v>
@@ -3960,7 +3961,7 @@
         <v>1010203002</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>20</v>
@@ -3989,7 +3990,7 @@
         <v>1010203002</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>20</v>
@@ -4018,7 +4019,7 @@
         <v>1010204001</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>21</v>
@@ -4039,7 +4040,7 @@
         <v>1010204001</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>21</v>
@@ -4068,7 +4069,7 @@
         <v>1010204001</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>21</v>
@@ -4097,7 +4098,7 @@
         <v>1010204001</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>21</v>
@@ -4126,7 +4127,7 @@
         <v>1010204001</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>21</v>
@@ -4155,7 +4156,7 @@
         <v>1010204001</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>21</v>
@@ -4185,7 +4186,7 @@
         <v>1010204002</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>21</v>
@@ -4205,7 +4206,7 @@
         <v>1010204002</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>21</v>
@@ -4234,7 +4235,7 @@
         <v>1010204002</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>21</v>
@@ -4263,7 +4264,7 @@
         <v>1010204002</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>21</v>
@@ -4292,7 +4293,7 @@
         <v>1010204002</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>21</v>
@@ -4322,7 +4323,7 @@
         <v>1010204002</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>21</v>
@@ -4351,10 +4352,10 @@
         <v>1010205001</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F64" s="1">
         <v>0.1</v>
@@ -4371,10 +4372,10 @@
         <v>1010205001</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F65" s="1">
         <v>0.125</v>
@@ -4383,7 +4384,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R65" s="1">
         <v>0.05</v>
@@ -4400,10 +4401,10 @@
         <v>1010205001</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F66" s="1">
         <v>0.15</v>
@@ -4412,7 +4413,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R66" s="1">
         <v>0.1</v>
@@ -4429,10 +4430,10 @@
         <v>1010205001</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F67" s="1">
         <v>0.17499999999999999</v>
@@ -4441,7 +4442,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R67" s="1">
         <v>0.15</v>
@@ -4459,10 +4460,10 @@
         <v>1010205001</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F68" s="1">
         <v>0.2</v>
@@ -4471,7 +4472,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R68" s="1">
         <v>0.2</v>
@@ -4488,10 +4489,10 @@
         <v>1010205001</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F69" s="1">
         <v>0.22500000000000001</v>
@@ -4500,7 +4501,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R69" s="1">
         <v>0.25</v>
@@ -4517,10 +4518,10 @@
         <v>1010205002</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F70" s="1">
         <v>0.1</v>
@@ -4537,10 +4538,10 @@
         <v>1010205002</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F71" s="1">
         <v>0.125</v>
@@ -4549,7 +4550,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R71" s="1">
         <v>0.05</v>
@@ -4566,10 +4567,10 @@
         <v>1010205002</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F72" s="1">
         <v>0.15</v>
@@ -4578,7 +4579,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R72" s="1">
         <v>0.1</v>
@@ -4596,10 +4597,10 @@
         <v>1010205002</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F73" s="1">
         <v>0.17499999999999999</v>
@@ -4608,7 +4609,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R73" s="1">
         <v>0.15</v>
@@ -4625,10 +4626,10 @@
         <v>1010205002</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F74" s="1">
         <v>0.2</v>
@@ -4637,7 +4638,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R74" s="1">
         <v>0.2</v>
@@ -4654,10 +4655,10 @@
         <v>1010205002</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F75" s="1">
         <v>0.22500000000000001</v>
@@ -4666,7 +4667,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R75" s="1">
         <v>0.25</v>
@@ -4683,7 +4684,7 @@
         <v>1010306001</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -4706,7 +4707,7 @@
         <v>1010306001</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E77" t="s">
         <v>17</v>
@@ -4735,7 +4736,7 @@
         <v>1010306001</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E78" t="s">
         <v>17</v>
@@ -4764,7 +4765,7 @@
         <v>1010306001</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
@@ -4793,7 +4794,7 @@
         <v>1010306001</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -4822,7 +4823,7 @@
         <v>1010306001</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E81" t="s">
         <v>17</v>
@@ -4851,7 +4852,7 @@
         <v>1010306002</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E82" t="s">
         <v>38</v>
@@ -4874,7 +4875,7 @@
         <v>1010306002</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E83" t="s">
         <v>18</v>
@@ -4903,7 +4904,7 @@
         <v>1010306002</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E84" t="s">
         <v>18</v>
@@ -4932,7 +4933,7 @@
         <v>1010306002</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E85" t="s">
         <v>18</v>
@@ -4961,7 +4962,7 @@
         <v>1010306002</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E86" t="s">
         <v>18</v>
@@ -4990,7 +4991,7 @@
         <v>1010306002</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
@@ -5019,7 +5020,7 @@
         <v>1010307001</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
@@ -5042,7 +5043,7 @@
         <v>1010307001</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -5071,7 +5072,7 @@
         <v>1010307001</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E90" t="s">
         <v>17</v>
@@ -5100,7 +5101,7 @@
         <v>1010307001</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E91" t="s">
         <v>17</v>
@@ -5129,7 +5130,7 @@
         <v>1010307001</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -5158,7 +5159,7 @@
         <v>1010307001</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
@@ -5187,7 +5188,7 @@
         <v>1010307002</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E94" t="s">
         <v>38</v>
@@ -5210,7 +5211,7 @@
         <v>1010307002</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E95" t="s">
         <v>18</v>
@@ -5239,7 +5240,7 @@
         <v>1010307002</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E96" t="s">
         <v>18</v>
@@ -5268,7 +5269,7 @@
         <v>1010307002</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E97" t="s">
         <v>18</v>
@@ -5297,7 +5298,7 @@
         <v>1010307002</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E98" t="s">
         <v>18</v>
@@ -5326,7 +5327,7 @@
         <v>1010307002</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E99" t="s">
         <v>18</v>
@@ -5355,7 +5356,7 @@
         <v>1010408001</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -5378,7 +5379,7 @@
         <v>1010408001</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -5407,7 +5408,7 @@
         <v>1010408001</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E102" t="s">
         <v>17</v>
@@ -5436,7 +5437,7 @@
         <v>1010408001</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E103" t="s">
         <v>17</v>
@@ -5465,7 +5466,7 @@
         <v>1010408001</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E104" t="s">
         <v>17</v>
@@ -5494,7 +5495,7 @@
         <v>1010408001</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E105" t="s">
         <v>17</v>
@@ -5523,7 +5524,7 @@
         <v>1010408002</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E106" t="s">
         <v>38</v>
@@ -5546,7 +5547,7 @@
         <v>1010408002</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E107" t="s">
         <v>18</v>
@@ -5575,7 +5576,7 @@
         <v>1010408002</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
@@ -5604,7 +5605,7 @@
         <v>1010408002</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E109" t="s">
         <v>18</v>
@@ -5633,7 +5634,7 @@
         <v>1010408002</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E110" t="s">
         <v>18</v>
@@ -5662,7 +5663,7 @@
         <v>1010408002</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E111" t="s">
         <v>18</v>
@@ -5779,37 +5780,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -5818,10 +5819,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -5830,7 +5831,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>2</v>
@@ -5839,16 +5840,16 @@
         <v>2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -5860,7 +5861,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -5872,7 +5873,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -5884,7 +5885,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -5895,7 +5896,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -5906,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -5917,7 +5918,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -5926,10 +5927,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -5938,10 +5939,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -5949,10 +5950,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -5960,10 +5961,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -5971,10 +5972,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -5983,10 +5984,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -5995,10 +5996,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -6006,10 +6007,10 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -6017,10 +6018,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -6028,10 +6029,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -6040,10 +6041,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -6051,10 +6052,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -6062,10 +6063,10 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -6073,10 +6074,10 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -6084,10 +6085,10 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -6096,10 +6097,10 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -6107,10 +6108,10 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -6118,10 +6119,10 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -6129,10 +6130,10 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -6140,10 +6141,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -6152,10 +6153,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -6163,10 +6164,10 @@
         <v>28</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -6174,10 +6175,10 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -6185,10 +6186,10 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -6196,10 +6197,10 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -6208,10 +6209,10 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -6219,10 +6220,10 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -6230,10 +6231,10 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -6241,10 +6242,10 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -6252,10 +6253,10 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -6264,10 +6265,10 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -6275,10 +6276,10 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -6286,10 +6287,10 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -6297,10 +6298,10 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -6308,10 +6309,10 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -6319,10 +6320,10 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -6330,10 +6331,10 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -6341,10 +6342,10 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -6352,10 +6353,10 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
@@ -6363,10 +6364,10 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
@@ -6374,10 +6375,10 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
@@ -6385,10 +6386,10 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
@@ -6430,10 +6431,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -6448,7 +6449,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>27</v>
@@ -6457,13 +6458,13 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -6472,7 +6473,7 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>5</v>
@@ -6487,7 +6488,7 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>6</v>
@@ -6502,7 +6503,7 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>7</v>
@@ -6516,7 +6517,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>8</v>
@@ -6530,7 +6531,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>9</v>
@@ -6544,7 +6545,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>10</v>
@@ -6642,10 +6643,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>33</v>
@@ -6675,10 +6676,10 @@
         <v>35</v>
       </c>
       <c r="N2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -6687,13 +6688,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>13</v>
@@ -6720,10 +6721,10 @@
         <v>13</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -6818,7 +6819,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>5</v>
@@ -6832,7 +6833,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -6846,7 +6847,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>7</v>
@@ -6860,7 +6861,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>8</v>
@@ -6875,7 +6876,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>9</v>
@@ -6889,7 +6890,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>10</v>
@@ -6901,7 +6902,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>5</v>
@@ -6915,7 +6916,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -6930,7 +6931,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>7</v>
@@ -6944,7 +6945,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>8</v>
@@ -6958,7 +6959,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>9</v>
@@ -6972,7 +6973,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>10</v>
@@ -6985,7 +6986,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>5</v>
@@ -6999,7 +7000,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -7013,7 +7014,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>7</v>
@@ -7027,7 +7028,7 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>8</v>
@@ -7042,7 +7043,7 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>9</v>
@@ -7056,7 +7057,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>10</v>
@@ -7068,7 +7069,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>5</v>
@@ -7082,7 +7083,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>6</v>
@@ -7097,7 +7098,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>7</v>
@@ -7111,7 +7112,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>8</v>
@@ -7125,7 +7126,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>9</v>
@@ -7139,7 +7140,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>10</v>
@@ -7152,7 +7153,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>5</v>
@@ -7166,7 +7167,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>6</v>
@@ -7180,7 +7181,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>7</v>
@@ -7194,7 +7195,7 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>8</v>
@@ -7208,7 +7209,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>9</v>
@@ -7222,7 +7223,7 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>10</v>
@@ -7234,7 +7235,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>5</v>
@@ -7248,7 +7249,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>6</v>
@@ -7262,7 +7263,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>7</v>
@@ -7276,7 +7277,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>8</v>
@@ -7290,7 +7291,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>9</v>
@@ -7304,7 +7305,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>10</v>
@@ -7316,7 +7317,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>5</v>
@@ -7330,7 +7331,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
@@ -7344,7 +7345,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>7</v>
@@ -7358,7 +7359,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>8</v>
@@ -7372,7 +7373,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>9</v>
@@ -7386,7 +7387,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>10</v>
@@ -7415,10 +7416,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="12"/>
@@ -7429,34 +7430,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -7659,10 +7660,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="12"/>
@@ -7673,49 +7674,49 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="1">
         <v>0.6</v>
@@ -7728,16 +7729,16 @@
         <v>0.3</v>
       </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D5" s="1">
         <v>0.8</v>
@@ -7750,16 +7751,16 @@
         <v>0.35</v>
       </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -7772,15 +7773,15 @@
         <v>0.22</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1">
         <v>1.2</v>
@@ -7793,15 +7794,15 @@
         <v>0.1</v>
       </c>
       <c r="G7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" t="s">
         <v>126</v>
-      </c>
-      <c r="C8" t="s">
-        <v>128</v>
       </c>
       <c r="D8" s="1">
         <v>1.4</v>
@@ -7814,7 +7815,7 @@
         <v>0.03</v>
       </c>
       <c r="G8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -7926,10 +7927,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>145</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>147</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -7942,53 +7943,53 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="J2" s="11"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7997,7 +7998,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D4" s="1">
         <v>800</v>
@@ -8024,7 +8025,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D5" s="1">
         <v>400</v>
@@ -8051,7 +8052,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -8077,7 +8078,7 @@
         <v>20001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1">
         <v>400</v>
@@ -8103,7 +8104,7 @@
         <v>20002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -8130,7 +8131,7 @@
         <v>20003</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8157,7 +8158,7 @@
         <v>30001</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="175">
   <si>
     <t>!Table</t>
   </si>
@@ -729,6 +729,30 @@
   </si>
   <si>
     <t>DualBlades</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSetAddress</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSet_DualBlades_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSet_RuneSword_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSet_CrossBow_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSet_DualPistols_01</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -1380,7 +1404,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1426,10 +1450,10 @@
     <col min="4" max="4" width="19.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.875" style="1" customWidth="1"/>
     <col min="13" max="13" width="23" style="1" bestFit="1" customWidth="1"/>
@@ -1476,9 +1500,10 @@
       <c r="F2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="O2" s="8"/>
@@ -1500,7 +1525,10 @@
       <c r="F3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="L3" s="8"/>
@@ -1524,6 +1552,9 @@
       <c r="F4" s="1">
         <v>1010101001</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="H4"/>
       <c r="J4" s="8"/>
       <c r="L4" s="8"/>
@@ -1547,6 +1578,9 @@
       <c r="F5" s="1">
         <v>1010101002</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="H5"/>
       <c r="J5" s="8"/>
       <c r="L5" s="8"/>
@@ -1570,6 +1604,9 @@
       <c r="F6" s="1">
         <v>1010101003</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="H6"/>
       <c r="J6" s="8"/>
       <c r="L6" s="8"/>
@@ -1592,6 +1629,9 @@
       </c>
       <c r="F7" s="1">
         <v>1010101004</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="H7"/>
       <c r="J7" s="8"/>

--- a/Shared/XLS/Equipment.xlsx
+++ b/Shared/XLS/Equipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="178">
   <si>
     <t>!Table</t>
   </si>
@@ -47,63 +47,63 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Mythic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemID_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipEnhance</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_ATK_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_MELEE_DAMAGE_BONUS_ADD</t>
@@ -113,19 +113,19 @@
   </si>
   <si>
     <t>OPT_MAX_HP_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_DEF_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_ATK_SPEED_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_CRIT_RATE_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -141,7 +141,7 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_DAMAGE_BONUS_ADD</t>
@@ -154,90 +154,90 @@
   </si>
   <si>
     <t>MaxLevel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemCnt_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemID_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemCnt_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemID_3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemCnt_3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ToGrade</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemID_4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemCnt_4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipPromotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_MAX_HP_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_RANGE_DAMAGE_BONUS_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RuneSword</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Ring</t>
   </si>
   <si>
     <t>Ring</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Amulet</t>
   </si>
   <si>
     <t>Amulet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Helmet</t>
   </si>
   <si>
     <t>Helmet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Armor</t>
   </si>
   <si>
     <t>Armor</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Boots</t>
   </si>
   <si>
     <t>Boots</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Gloves</t>
@@ -247,14 +247,14 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ItemGrade</t>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Opt1_ID</t>
@@ -321,58 +321,54 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EquipOption</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipOptionGroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
   </si>
   <si>
     <t>Relic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Category</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostCurrencyID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Currency</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostCurrencyValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MaxGrade</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemID_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemCnt_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemMult_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CostItemID_2</t>
@@ -385,46 +381,46 @@
   </si>
   <si>
     <t>CostCurrencyMult</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipQuality</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Relic</t>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!EquipSlotTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipSlotType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>UnlockOpt_MinVal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>UnlockOpt_MaxVal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>FromGrade</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!EquipSlotTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -452,15 +448,15 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EnhanceTier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tier_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tier_2</t>
@@ -479,19 +475,19 @@
   </si>
   <si>
     <t>EquipEnhanceTier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!EquipEnhanceTier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipPurity</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!EquipPurity</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -519,18 +515,18 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Purity_1</t>
@@ -561,43 +557,43 @@
       </rPr>
       <t>isplayName</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>S</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>B</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>C</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>D</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OptionMultiplier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>AssignWeight</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CalcRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ColorHex</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>#FF4D4D</t>
@@ -616,15 +612,15 @@
   </si>
   <si>
     <t>MinValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MaxValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!EquipEnhanceTier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -641,15 +637,15 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MinLevel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipGradeWeight</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
@@ -677,99 +673,123 @@
   </si>
   <si>
     <t>CrossBow</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DualPistols</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RuneSword</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CrossBow</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DualPistols</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!WeaponType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!EquipSlotTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>EquipSlotTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>OPT_MOVE_SPEED_ADD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DualBlades</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponSetAddress</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponSet_DualBlades_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponSet_RuneSword_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponSet_CrossBow_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WeaponSet_DualPistols_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DualBlades</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloves</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amulet</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relic</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipOption</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -958,11 +978,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,69 +994,69 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1319,7 +1339,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1345,13 +1365,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1367,7 +1387,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -1385,12 +1405,12 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1398,13 +1418,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1414,12 +1434,12 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1434,7 +1454,7 @@
       <c r="C18" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1489,19 +1509,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>85</v>
+      <c r="E2" s="20" t="s">
+        <v>84</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I2" s="8"/>
       <c r="L2" s="8"/>
@@ -1514,19 +1534,19 @@
         <v>2</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="23" t="s">
         <v>160</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>161</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -1541,10 +1561,10 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>75</v>
@@ -1553,7 +1573,7 @@
         <v>1010101001</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H4"/>
       <c r="J4" s="8"/>
@@ -1567,10 +1587,10 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>75</v>
@@ -1579,7 +1599,7 @@
         <v>1010101002</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H5"/>
       <c r="J5" s="8"/>
@@ -1593,10 +1613,10 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>75</v>
@@ -1605,7 +1625,7 @@
         <v>1010101003</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H6"/>
       <c r="J6" s="8"/>
@@ -1619,10 +1639,10 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>75</v>
@@ -1631,7 +1651,7 @@
         <v>1010101004</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7"/>
       <c r="J7" s="8"/>
@@ -1893,7 +1913,7 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>75</v>
@@ -1913,7 +1933,7 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>75</v>
@@ -2150,7 +2170,7 @@
       <c r="O42" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2186,8 +2206,8 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>77</v>
+      <c r="B1" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -2255,10 +2275,10 @@
         <v>67</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -2270,7 +2290,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>68</v>
@@ -2350,9 +2370,15 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="P4" s="8"/>
-      <c r="Q4"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
+      <c r="Q4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="11">
+        <v>5</v>
+      </c>
+      <c r="S4" s="11">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
@@ -2597,9 +2623,15 @@
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="P10" s="8"/>
-      <c r="Q10"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
+      <c r="Q10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" s="11">
+        <v>5</v>
+      </c>
+      <c r="S10" s="11">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
@@ -2847,9 +2879,15 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="P16" s="8"/>
-      <c r="Q16"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
+      <c r="Q16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R16" s="11">
+        <v>5</v>
+      </c>
+      <c r="S16" s="11">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
@@ -3096,9 +3134,15 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="P22" s="8"/>
-      <c r="Q22"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
+      <c r="Q22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="11">
+        <v>5</v>
+      </c>
+      <c r="S22" s="11">
+        <v>10</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
@@ -3339,9 +3383,15 @@
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="P28" s="8"/>
-      <c r="Q28"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
+      <c r="Q28" t="s">
+        <v>19</v>
+      </c>
+      <c r="R28" s="11">
+        <v>50</v>
+      </c>
+      <c r="S28" s="11">
+        <v>100</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
@@ -3537,9 +3587,15 @@
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
       <c r="P34" s="8"/>
-      <c r="Q34"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
+      <c r="Q34" t="s">
+        <v>19</v>
+      </c>
+      <c r="R34" s="11">
+        <v>50</v>
+      </c>
+      <c r="S34" s="11">
+        <v>100</v>
+      </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
@@ -3724,6 +3780,15 @@
       <c r="G40" s="1">
         <v>0.5</v>
       </c>
+      <c r="Q40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R40" s="1">
+        <v>7</v>
+      </c>
+      <c r="S40" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
@@ -3899,6 +3964,15 @@
       </c>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
+      <c r="Q46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R46" s="1">
+        <v>7</v>
+      </c>
+      <c r="S46" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
@@ -4070,6 +4144,15 @@
       <c r="G52" s="1">
         <v>1E-3</v>
       </c>
+      <c r="Q52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
@@ -4237,6 +4320,15 @@
       <c r="G58" s="1">
         <v>1E-3</v>
       </c>
+      <c r="Q58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R58" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B59" s="1">
@@ -4395,13 +4487,22 @@
         <v>70</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F64" s="1">
         <v>0.1</v>
       </c>
       <c r="G64" s="1">
         <v>1E-3</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R64" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0.05</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
@@ -4415,7 +4516,7 @@
         <v>71</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F65" s="1">
         <v>0.125</v>
@@ -4424,7 +4525,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R65" s="1">
         <v>0.05</v>
@@ -4444,7 +4545,7 @@
         <v>72</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F66" s="1">
         <v>0.15</v>
@@ -4453,7 +4554,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R66" s="1">
         <v>0.1</v>
@@ -4473,7 +4574,7 @@
         <v>73</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F67" s="1">
         <v>0.17499999999999999</v>
@@ -4482,7 +4583,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R67" s="1">
         <v>0.15</v>
@@ -4503,7 +4604,7 @@
         <v>74</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F68" s="1">
         <v>0.2</v>
@@ -4512,7 +4613,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R68" s="1">
         <v>0.2</v>
@@ -4532,7 +4633,7 @@
         <v>75</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F69" s="1">
         <v>0.22500000000000001</v>
@@ -4541,7 +4642,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R69" s="1">
         <v>0.25</v>
@@ -4561,13 +4662,22 @@
         <v>70</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F70" s="1">
         <v>0.1</v>
       </c>
       <c r="G70" s="1">
         <v>1E-3</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R70" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0.05</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
@@ -4581,7 +4691,7 @@
         <v>71</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F71" s="1">
         <v>0.125</v>
@@ -4590,7 +4700,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R71" s="1">
         <v>0.05</v>
@@ -4610,7 +4720,7 @@
         <v>72</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F72" s="1">
         <v>0.15</v>
@@ -4619,7 +4729,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R72" s="1">
         <v>0.1</v>
@@ -4640,7 +4750,7 @@
         <v>73</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F73" s="1">
         <v>0.17499999999999999</v>
@@ -4649,7 +4759,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R73" s="1">
         <v>0.15</v>
@@ -4669,7 +4779,7 @@
         <v>74</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F74" s="1">
         <v>0.2</v>
@@ -4678,7 +4788,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R74" s="1">
         <v>0.2</v>
@@ -4698,7 +4808,7 @@
         <v>75</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F75" s="1">
         <v>0.22500000000000001</v>
@@ -4707,7 +4817,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R75" s="1">
         <v>0.25</v>
@@ -4735,9 +4845,15 @@
       <c r="G76" s="11">
         <v>0.01</v>
       </c>
-      <c r="Q76"/>
-      <c r="R76" s="11"/>
-      <c r="S76" s="11"/>
+      <c r="Q76" t="s">
+        <v>17</v>
+      </c>
+      <c r="R76" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="S76" s="11">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
@@ -4903,9 +5019,15 @@
       <c r="G82" s="11">
         <v>0.01</v>
       </c>
-      <c r="Q82"/>
-      <c r="R82" s="11"/>
-      <c r="S82" s="11"/>
+      <c r="Q82" t="s">
+        <v>38</v>
+      </c>
+      <c r="R82" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="S82" s="11">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="83" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B83" s="1">
@@ -5071,9 +5193,15 @@
       <c r="G88" s="11">
         <v>0.01</v>
       </c>
-      <c r="Q88"/>
-      <c r="R88" s="11"/>
-      <c r="S88" s="11"/>
+      <c r="Q88" t="s">
+        <v>17</v>
+      </c>
+      <c r="R88" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="S88" s="11">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="89" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B89" s="1">
@@ -5239,9 +5367,15 @@
       <c r="G94" s="11">
         <v>0.01</v>
       </c>
-      <c r="Q94"/>
-      <c r="R94" s="11"/>
-      <c r="S94" s="11"/>
+      <c r="Q94" t="s">
+        <v>38</v>
+      </c>
+      <c r="R94" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="S94" s="11">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B95" s="1">
@@ -5407,9 +5541,15 @@
       <c r="G100" s="11">
         <v>0.01</v>
       </c>
-      <c r="Q100"/>
-      <c r="R100" s="11"/>
-      <c r="S100" s="11"/>
+      <c r="Q100" t="s">
+        <v>17</v>
+      </c>
+      <c r="R100" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="S100" s="11">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="101" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B101" s="1">
@@ -5575,9 +5715,15 @@
       <c r="G106" s="11">
         <v>0.01</v>
       </c>
-      <c r="Q106"/>
-      <c r="R106" s="11"/>
-      <c r="S106" s="11"/>
+      <c r="Q106" t="s">
+        <v>38</v>
+      </c>
+      <c r="R106" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="S106" s="11">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="107" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B107" s="1">
@@ -5775,7 +5921,7 @@
       <c r="E121" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5820,37 +5966,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="L2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -5859,10 +6005,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -5871,7 +6017,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>2</v>
@@ -5880,16 +6026,16 @@
         <v>2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -5901,7 +6047,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -5913,7 +6059,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -5925,7 +6071,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -5936,7 +6082,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -5947,7 +6093,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -5958,7 +6104,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -5970,7 +6116,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -5982,7 +6128,7 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -5993,7 +6139,7 @@
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -6004,7 +6150,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -6015,7 +6161,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -6027,7 +6173,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -6039,7 +6185,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -6050,7 +6196,7 @@
         <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -6061,7 +6207,7 @@
         <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -6072,7 +6218,7 @@
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -6084,7 +6230,7 @@
         <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -6095,7 +6241,7 @@
         <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -6106,7 +6252,7 @@
         <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -6117,7 +6263,7 @@
         <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -6128,7 +6274,7 @@
         <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -6140,7 +6286,7 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -6151,7 +6297,7 @@
         <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -6162,7 +6308,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -6173,7 +6319,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -6184,7 +6330,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -6196,7 +6342,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -6207,7 +6353,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -6218,7 +6364,7 @@
         <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -6229,7 +6375,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -6240,7 +6386,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -6252,7 +6398,7 @@
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -6263,7 +6409,7 @@
         <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -6274,7 +6420,7 @@
         <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -6285,7 +6431,7 @@
         <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -6296,7 +6442,7 @@
         <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -6308,7 +6454,7 @@
         <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -6319,7 +6465,7 @@
         <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -6330,7 +6476,7 @@
         <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -6341,7 +6487,7 @@
         <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -6352,7 +6498,7 @@
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -6363,7 +6509,7 @@
         <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -6371,10 +6517,10 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -6382,10 +6528,10 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -6393,10 +6539,10 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
@@ -6404,10 +6550,10 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
@@ -6415,10 +6561,10 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
@@ -6426,10 +6572,10 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
@@ -6451,7 +6597,7 @@
       <c r="D57"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6470,11 +6616,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>112</v>
+      <c r="A1" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>111</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -6489,7 +6635,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>27</v>
@@ -6498,10 +6644,10 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>52</v>
@@ -6513,7 +6659,7 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>5</v>
@@ -6528,7 +6674,7 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>6</v>
@@ -6543,7 +6689,7 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>7</v>
@@ -6557,7 +6703,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>8</v>
@@ -6571,7 +6717,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>9</v>
@@ -6585,7 +6731,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>10</v>
@@ -6638,7 +6784,7 @@
       <c r="A40" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6683,10 +6829,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>33</v>
@@ -6716,10 +6862,10 @@
         <v>35</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -6728,13 +6874,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>13</v>
@@ -6761,7 +6907,7 @@
         <v>13</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>52</v>
@@ -7357,7 +7503,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>5</v>
@@ -7371,7 +7517,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
@@ -7385,7 +7531,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>7</v>
@@ -7399,7 +7545,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>8</v>
@@ -7413,7 +7559,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>9</v>
@@ -7427,7 +7573,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>10</v>
@@ -7435,7 +7581,7 @@
       <c r="E51" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7455,13 +7601,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="22"/>
+      <c r="A1" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="21"/>
       <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -7470,16 +7616,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -7497,7 +7643,7 @@
         <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -7678,7 +7824,7 @@
       <c r="A34" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7699,13 +7845,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="22"/>
+      <c r="A1" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="21"/>
       <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7714,28 +7860,28 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>69</v>
@@ -7744,19 +7890,19 @@
         <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="1">
         <v>0.6</v>
@@ -7769,16 +7915,16 @@
         <v>0.3</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" s="1">
         <v>0.8</v>
@@ -7791,16 +7937,16 @@
         <v>0.35</v>
       </c>
       <c r="G5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -7813,15 +7959,15 @@
         <v>0.22</v>
       </c>
       <c r="G6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1">
         <v>1.2</v>
@@ -7834,15 +7980,15 @@
         <v>0.1</v>
       </c>
       <c r="G7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="1">
         <v>1.4</v>
@@ -7855,7 +8001,7 @@
         <v>0.03</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -7943,7 +8089,7 @@
       <c r="A34" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7966,15 +8112,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="A1" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
       <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -7983,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>70</v>
@@ -8011,7 +8157,7 @@
         <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>51</v>
@@ -8038,7 +8184,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D4" s="1">
         <v>800</v>
@@ -8065,7 +8211,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D5" s="1">
         <v>400</v>
@@ -8092,7 +8238,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -8118,7 +8264,7 @@
         <v>20001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="1">
         <v>400</v>
@@ -8144,7 +8290,7 @@
         <v>20002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -8171,7 +8317,7 @@
         <v>20003</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8198,7 +8344,7 @@
         <v>30001</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8306,7 +8452,7 @@
       <c r="A34" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>